--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,92 +531,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>70.81</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.2975</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>L19516436</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,92 +635,84 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.4512</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>L19516436</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,110 +739,334 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,7 +542,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,15 +643,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -659,7 +663,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,92 +747,84 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>70.81</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.2975</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>L19516436</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,92 +851,84 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1.4512</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>L19516436</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,110 +955,334 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,94 +651,86 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.0525</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>FC Porto vs Alverca</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>FC Porto</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>L19516476</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -755,15 +755,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -771,7 +775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,7 +870,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -928,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,92 +963,84 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.2975</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>L19516436</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1097,32 +1097,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785703082</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>3.361345</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,110 +1179,222 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,23 +643,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -667,7 +671,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -690,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -755,19 +763,15 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -775,11 +779,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -867,15 +867,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -883,7 +887,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -891,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -974,7 +982,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1040,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,27 +1075,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1095,11 +1099,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,12 +1179,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1209,32 +1209,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785703082</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>3.361345</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,110 +1291,222 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,19 +651,15 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -671,11 +667,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,23 +747,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -779,7 +775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -802,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,23 +971,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -995,7 +999,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1003,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,31 +1083,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1122,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,12 +1210,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1209,7 +1225,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1219,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,27 +1307,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1319,11 +1331,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1331,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1384,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,110 +1411,982 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.0513</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FC Porto vs Alverca</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19516476</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1786025695</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1786294800</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.4125</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1786015629</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>19.345455</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785807147</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.0525</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FC Porto vs Alverca</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19516476</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785805367</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1786294800</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>28.761905</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>70.81</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785793268</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785792146</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,23 +643,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -667,7 +671,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -755,19 +763,15 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -775,11 +779,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1315,15 +1315,19 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1331,7 +1335,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1339,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,27 +1419,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1439,11 +1443,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1451,27 +1451,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1563,27 +1563,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1608,17 +1608,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,23 +1635,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1659,7 +1663,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1682,7 +1690,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1712,7 +1720,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1722,7 +1730,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1739,7 +1747,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1747,19 +1755,15 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1767,11 +1771,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1779,27 +1779,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,7 +1851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,15 +1859,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1875,7 +1879,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1883,27 +1891,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1928,17 +1936,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,7 +1963,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1966,7 +1974,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2032,7 +2040,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2042,7 +2050,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,27 +2067,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2087,11 +2091,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,12 +2171,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2201,32 +2201,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785703082</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>3.361345</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,110 +2283,222 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,23 +755,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -779,7 +783,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -787,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -867,19 +875,15 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -887,11 +891,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1347,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1427,15 +1427,19 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1443,7 +1447,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1451,27 +1459,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1504,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,27 +1531,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1551,11 +1555,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1563,27 +1563,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1608,17 +1608,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1675,27 +1675,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,23 +1747,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1771,7 +1775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1794,7 +1802,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1824,7 +1832,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1834,7 +1842,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,7 +1859,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,19 +1867,15 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1879,11 +1883,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1891,27 +1891,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1971,15 +1971,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1987,7 +1991,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1995,27 +2003,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2040,17 +2048,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,7 +2075,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2078,7 +2086,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2144,7 +2152,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2162,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,27 +2179,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2199,11 +2203,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2313,32 +2313,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785703082</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>3.361345</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,110 +2395,222 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,27 +755,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -783,11 +779,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -795,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,23 +859,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -899,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,27 +963,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -999,11 +987,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1011,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,27 +1067,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1111,11 +1091,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1123,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,27 +1171,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1223,26 +1195,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Estrela Amadora</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Sporting Clube De Portugal CP</t>
@@ -1280,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,39 +1275,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1347,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,27 +1379,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1447,11 +1403,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1459,27 +1411,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1504,17 +1456,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,23 +1483,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1578,7 +1530,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1608,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1618,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,27 +1587,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1663,11 +1611,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1675,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,27 +1691,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1775,11 +1715,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1787,27 +1723,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1832,17 +1768,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1859,23 +1795,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1891,27 +1827,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1936,17 +1872,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,27 +1899,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1991,11 +1923,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2003,27 +1931,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2048,17 +1976,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,23 +2003,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2099,7 +2031,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2152,7 +2088,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2162,7 +2098,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2179,23 +2115,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2203,7 +2143,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2211,27 +2155,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2256,17 +2200,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,12 +2227,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2298,12 +2242,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2313,7 +2257,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2282,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2368,7 +2312,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2378,7 +2322,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,12 +2339,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2410,12 +2354,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2425,32 +2369,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2480,7 +2424,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2490,7 +2434,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,110 +2451,1750 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>165.96</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.4875</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Vitoria Guimaraes</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>FC Arouca</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19516475</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1786049379</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1786208400</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>340.430769</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.10054</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.2925</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1786048863</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>3.76253</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.2925</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1786048862</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>34.188034</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>19.0949</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.0662</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19516479</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1786045554</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1786217400</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>288.224906</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.4937</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1786045527</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>6.622785</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10.12292</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.0362</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs Academico Viseu</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19551968</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1786045134</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1786303800</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>279.252966</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20.58</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.2125</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19516479</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1786043934</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1786217400</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>96.847059</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1.025</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.0513</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>FC Porto vs Alverca</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19516476</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1786025695</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1786294800</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.4125</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1786015629</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>19.345455</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785807147</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.0525</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>FC Porto vs Alverca</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19516476</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785805367</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1786294800</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>28.761905</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>70.81</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785793268</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785792146</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,11 +555,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +650,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +665,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,23 +747,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -779,7 +775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,23 +859,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -883,7 +887,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -936,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1040,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1067,7 +1075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1144,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1171,7 +1179,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1275,7 +1283,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1352,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1379,7 +1387,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1456,7 +1464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1483,7 +1491,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1560,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1587,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1664,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1691,7 +1699,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1768,7 +1776,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1795,7 +1803,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1872,7 +1880,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1899,7 +1907,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,7 +1918,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1976,7 +1984,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1986,7 +1994,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,27 +2011,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2031,11 +2035,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2043,27 +2043,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,27 +2115,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2143,11 +2139,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2155,27 +2147,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2200,17 +2192,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,7 +2219,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2242,7 +2234,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2312,7 +2304,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2322,7 +2314,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2339,12 +2331,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2354,12 +2346,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2369,7 +2361,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2379,27 +2371,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2424,17 +2416,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2451,23 +2443,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2475,7 +2471,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2483,27 +2483,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,12 +2555,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,27 +2667,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2695,11 +2691,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2707,27 +2699,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2752,17 +2744,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,12 +2771,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2794,12 +2786,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2809,7 +2801,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2819,27 +2811,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2864,17 +2856,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,7 +2883,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2906,22 +2898,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2946,7 +2938,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2976,7 +2968,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2986,7 +2978,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,7 +2995,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3018,12 +3010,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3033,7 +3025,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3043,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3088,17 +3080,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,31 +3107,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3147,27 +3147,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,12 +3219,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3259,27 +3259,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3304,17 +3304,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,27 +3331,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3359,11 +3355,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3371,27 +3363,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3416,17 +3408,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,23 +3435,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3467,7 +3463,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3475,27 +3475,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3520,17 +3520,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3587,27 +3587,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3632,17 +3632,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3670,7 +3670,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,7 +3763,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3771,15 +3771,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3787,7 +3791,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3795,27 +3803,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3840,17 +3848,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,27 +3875,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3895,11 +3899,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,27 +3979,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4007,34 +4003,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4064,7 +4056,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4074,7 +4066,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4091,110 +4083,334 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
+          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.07999</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786085661</t>
+          <t>1786090860</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.93786</t>
+          <t>25.350211</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
+          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786082857</t>
+          <t>1786089858</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>86.956522</t>
+          <t>11.019284</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,27 +755,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -775,11 +779,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,23 +971,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -995,7 +999,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1048,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,23 +1083,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1099,7 +1111,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1152,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1256,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1283,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1360,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1387,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1464,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1491,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1568,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1595,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1672,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1699,7 +1715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1776,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1803,7 +1819,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1880,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1907,7 +1923,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1984,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2011,7 +2027,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2088,7 +2104,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2115,7 +2131,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2126,7 +2142,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2192,7 +2208,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2202,7 +2218,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2219,27 +2235,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2247,11 +2259,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2259,27 +2267,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2304,17 +2312,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,27 +2339,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2359,11 +2363,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2371,27 +2371,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,7 +2443,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,12 +2555,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2595,27 +2595,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,23 +2667,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2691,7 +2695,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2699,27 +2707,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2744,17 +2752,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,12 +2779,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2786,12 +2794,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2801,7 +2809,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2826,7 +2834,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2856,7 +2864,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2866,7 +2874,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,27 +2891,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2911,11 +2915,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2923,27 +2923,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,12 +2995,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3035,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,7 +3107,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,7 +3219,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3259,27 +3259,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3304,17 +3304,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,31 +3331,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3363,27 +3371,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3408,17 +3416,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3435,12 +3443,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3450,12 +3458,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3465,7 +3473,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3475,27 +3483,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3520,17 +3528,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,27 +3555,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3575,11 +3579,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3587,27 +3587,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3632,17 +3632,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,23 +3659,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3683,7 +3687,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3691,27 +3699,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3736,17 +3744,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,12 +3771,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3778,12 +3786,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3793,7 +3801,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3803,27 +3811,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3848,17 +3856,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3875,7 +3883,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3886,7 +3894,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3952,7 +3960,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3962,7 +3970,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,7 +3987,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3987,15 +3995,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4003,7 +4015,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4011,27 +4027,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4056,17 +4072,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,27 +4099,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4111,11 +4123,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4138,7 +4146,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4168,7 +4176,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4178,7 +4186,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4195,27 +4203,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4223,34 +4227,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,110 +4307,334 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
+          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786090860</t>
+          <t>1786112735</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>25.350211</t>
+          <t>3.088803</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
+          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,39 +658,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786089858</t>
+          <t>1786090860</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11.019284</t>
+          <t>25.350211</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
+          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.07999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -787,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786085661</t>
+          <t>1786089858</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4.93786</t>
+          <t>11.019284</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,27 +867,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -887,11 +891,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>FC Arouca</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786082857</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>86.956522</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,23 +1195,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1219,7 +1223,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1272,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1376,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1403,7 +1411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1480,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1507,7 +1515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1584,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1611,7 +1619,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1688,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1715,7 +1723,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1792,7 +1800,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1819,7 +1827,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1896,7 +1904,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1923,7 +1931,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2000,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2027,7 +2035,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2104,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2131,7 +2139,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2208,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2235,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2312,7 +2320,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2339,7 +2347,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2350,7 +2358,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2416,7 +2424,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2426,7 +2434,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,27 +2451,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2471,11 +2475,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2483,27 +2483,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,12 +2555,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2595,27 +2595,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2707,27 +2707,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2752,17 +2752,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,7 +2779,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,23 +2891,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2915,7 +2919,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2923,27 +2931,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2968,17 +2976,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,7 +3003,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3003,19 +3011,15 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3023,11 +3027,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3035,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,12 +3219,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3259,27 +3259,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3304,17 +3304,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,12 +3331,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3346,22 +3346,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3371,27 +3371,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,12 +3443,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3458,22 +3458,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3483,27 +3483,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3528,17 +3528,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3563,15 +3563,19 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3579,7 +3583,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3587,27 +3595,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3632,17 +3640,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,27 +3667,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3687,11 +3691,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3699,27 +3699,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3744,17 +3744,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3811,27 +3811,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3856,17 +3856,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3883,23 +3883,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3907,7 +3911,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3930,7 +3938,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3960,7 +3968,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3970,7 +3978,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3987,7 +3995,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3995,19 +4003,15 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4015,11 +4019,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4027,27 +4027,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,7 +4099,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4107,15 +4107,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4123,7 +4127,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4131,27 +4139,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4176,17 +4184,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4203,7 +4211,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4214,7 +4222,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4280,7 +4288,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4290,7 +4298,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,27 +4315,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4335,11 +4339,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,12 +4419,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4449,32 +4449,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785703082</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>3.361345</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4531,110 +4531,222 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
+          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786112735</t>
+          <t>1786114912</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.088803</t>
+          <t>7.363636</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,27 +643,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
+          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>64.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -671,11 +667,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -698,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786090860</t>
+          <t>1786114872</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>25.350211</t>
+          <t>104.192385</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
+          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,39 +762,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -810,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786089858</t>
+          <t>1786112735</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>11.019284</t>
+          <t>3.088803</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,23 +859,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
+          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.07999</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -891,7 +887,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -899,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786085661</t>
+          <t>1786090860</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>4.93786</t>
+          <t>25.350211</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
+          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786082857</t>
+          <t>1786089858</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>86.956522</t>
+          <t>11.019284</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,27 +1083,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1111,11 +1107,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1123,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1210,12 +1202,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1225,7 +1217,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1272,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,23 +1299,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1331,7 +1327,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,23 +1411,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1435,7 +1439,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1488,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1592,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1619,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1696,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1723,7 +1731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1800,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1827,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1904,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1931,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2008,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2035,7 +2043,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2112,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2139,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2216,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2243,7 +2251,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2320,7 +2328,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2347,7 +2355,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2424,7 +2432,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2451,7 +2459,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2462,7 +2470,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2528,7 +2536,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2538,7 +2546,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,27 +2563,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2583,11 +2587,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2595,27 +2595,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,27 +2667,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2695,11 +2691,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2707,27 +2699,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2752,17 +2744,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,7 +2771,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2794,7 +2786,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2864,7 +2856,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2874,7 +2866,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,12 +2883,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2906,12 +2898,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2921,7 +2913,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2931,27 +2923,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2976,17 +2968,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,23 +2995,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3027,7 +3023,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3035,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,27 +3219,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3247,11 +3243,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3259,27 +3251,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3304,17 +3296,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,12 +3323,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3346,12 +3338,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3361,7 +3353,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3371,27 +3363,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3416,17 +3408,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,7 +3435,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3458,22 +3450,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3498,7 +3490,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3528,7 +3520,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3538,7 +3530,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3555,7 +3547,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3570,12 +3562,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3585,7 +3577,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3595,27 +3587,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3640,17 +3632,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3667,31 +3659,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3699,27 +3699,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3744,17 +3744,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3811,27 +3811,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3856,17 +3856,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3883,27 +3883,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3911,11 +3907,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3923,27 +3915,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3968,17 +3960,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3995,23 +3987,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4019,7 +4015,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4027,27 +4027,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,12 +4099,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4139,27 +4139,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4184,17 +4184,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4211,7 +4211,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4222,7 +4222,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,7 +4315,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4323,15 +4323,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4339,7 +4343,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4347,27 +4355,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4392,17 +4400,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,27 +4427,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4447,11 +4451,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4531,27 +4531,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4559,34 +4555,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4616,7 +4608,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4626,7 +4618,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4643,110 +4635,334 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
+          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>4.16999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.6787</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,11 +555,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Casa Pia</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786114912</t>
+          <t>1786129160</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>7.363636</t>
+          <t>6.143632</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
+          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>64.99</t>
+          <t>25.5377</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -690,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786114872</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>104.192385</t>
+          <t>48.527696</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,54 +739,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
+          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20.42793</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -802,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786112735</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.088803</t>
+          <t>38.817919</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
+          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -867,31 +851,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -914,7 +890,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786090860</t>
+          <t>1786128768</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>25.350211</t>
+          <t>9.691211</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,54 +947,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
+          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -1026,7 +994,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786089858</t>
+          <t>1786128742</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>11.019284</t>
+          <t>46.645012</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,31 +1051,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
+          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.07999</t>
+          <t>10.60893</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Estoril 0</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1115,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786085661</t>
+          <t>1786128656</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4.93786</t>
+          <t>21.650878</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,12 +1163,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
+          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1202,22 +1178,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1227,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1272,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786082857</t>
+          <t>1786128630</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>86.956522</t>
+          <t>6.791171</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,12 +1275,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1314,22 +1290,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>64.79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1339,27 +1315,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1360,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786128598</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,12 +1387,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1426,12 +1402,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1441,7 +1417,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1451,27 +1427,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1472,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786127300</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>40.939394</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,31 +1499,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1555,27 +1539,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1600,17 +1584,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>7.548872</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,31 +1611,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1659,27 +1651,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1696,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>4.325359</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,23 +1723,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.1825</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1763,27 +1755,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1808,17 +1800,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786126618</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>117.808219</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,31 +1827,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786124013</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>16.761905</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,23 +1939,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>38.34</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1971,27 +1971,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786123790</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>56.382353</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,31 +2043,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2075,27 +2083,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,17 +2128,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786123308</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>6.247619</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,23 +2155,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2171,7 +2183,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2179,27 +2195,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2224,17 +2240,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786114912</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>7.363636</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,23 +2267,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>64.99</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2283,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2328,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786114872</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>104.192385</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,23 +2371,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2379,7 +2399,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2387,27 +2411,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2432,17 +2456,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786112735</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>3.088803</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,23 +2483,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2483,7 +2511,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2491,27 +2523,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2536,17 +2568,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786090860</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>25.350211</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,31 +2595,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2595,27 +2635,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2640,17 +2680,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786089858</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>11.019284</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,23 +2707,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2699,27 +2739,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2744,17 +2784,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,12 +2811,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2786,12 +2826,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2801,7 +2841,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2811,27 +2851,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2856,17 +2896,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,12 +2923,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2898,12 +2938,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2913,7 +2953,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2923,27 +2963,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2968,17 +3008,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,12 +3035,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3010,12 +3050,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3025,7 +3065,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3035,27 +3075,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3080,17 +3120,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,27 +3147,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3135,11 +3171,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3147,27 +3179,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3192,17 +3224,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,23 +3251,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3251,27 +3283,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3296,17 +3328,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,27 +3355,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3351,11 +3379,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3363,27 +3387,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3408,17 +3432,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3435,27 +3459,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3463,11 +3483,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3475,27 +3491,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3520,17 +3536,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,27 +3563,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3575,26 +3587,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Estrela Amadora</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Sporting Clube De Portugal CP</t>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3642,7 +3650,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,39 +3667,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3699,27 +3699,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3744,17 +3744,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,27 +3771,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3799,11 +3795,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3811,27 +3803,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3856,17 +3848,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3883,23 +3875,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3930,7 +3922,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3960,7 +3952,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3970,7 +3962,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3987,27 +3979,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4015,11 +4003,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4027,27 +4011,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4072,17 +4056,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,27 +4083,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4127,11 +4107,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4139,27 +4115,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4184,17 +4160,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4211,23 +4187,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4243,27 +4219,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4288,17 +4264,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,27 +4291,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4343,11 +4315,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4355,27 +4323,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4400,17 +4368,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4427,23 +4395,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4451,7 +4423,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4504,7 +4480,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4514,7 +4490,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4531,23 +4507,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4555,7 +4535,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4563,27 +4547,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4608,17 +4592,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4635,12 +4619,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4650,12 +4634,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4665,7 +4649,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4690,7 +4674,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4720,7 +4704,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4730,7 +4714,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4747,12 +4731,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4762,12 +4746,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4777,32 +4761,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4832,7 +4816,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4842,7 +4826,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4859,110 +4843,1750 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>165.96</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.4875</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Vitoria Guimaraes</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>FC Arouca</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19516475</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1786049379</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1786208400</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>340.430769</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.10054</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.2925</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1786048863</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>3.76253</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.2925</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1786048862</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>34.188034</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>19.0949</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.0662</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19516479</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1786045554</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1786217400</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>288.224906</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.4937</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1786045527</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>6.622785</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>10.12292</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.0362</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs Academico Viseu</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19551968</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1786045134</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1786303800</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>279.252966</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20.58</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.2125</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19516479</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1786043934</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1786217400</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>96.847059</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1.025</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.0513</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>FC Porto vs Alverca</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19516476</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1786025695</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1786294800</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.4125</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1786015629</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>19.345455</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785807147</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.0525</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>FC Porto vs Alverca</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19516476</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785805367</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1786294800</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>28.761905</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>70.81</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785793268</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1785792146</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
+          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.16999</t>
+          <t>91.02352</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6787</t>
+          <t>1.4688</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786129160</t>
+          <t>1786135995</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6.143632</t>
+          <t>194.183509</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
+          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,12 +646,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25.5377</t>
+          <t>902.64812</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786128775</t>
+          <t>1786135994</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>48.527696</t>
+          <t>1930.798118</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
+          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20.42793</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786128775</t>
+          <t>1786135800</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>38.817919</t>
+          <t>155.339806</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,36 +843,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
+          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.99999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.6488</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
@@ -890,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -920,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786128768</t>
+          <t>1786135027</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>9.691211</t>
+          <t>9.248539</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +955,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
+          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.2475</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -994,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1024,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786128742</t>
+          <t>1786134086</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>46.645012</t>
+          <t>9.010101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,67 +1059,59 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
+          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.60893</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Estoril 0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786128656</t>
+          <t>1786132603</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>21.650878</t>
+          <t>134.757282</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,39 +1163,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
+          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1218,7 +1210,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1248,7 +1240,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786128630</t>
+          <t>1786131718</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1250,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>6.791171</t>
+          <t>91.925466</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,12 +1267,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
+          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1290,22 +1282,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>64.79</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.2525</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1330,7 +1322,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1360,7 +1352,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786128598</t>
+          <t>1786130523</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>552.475248</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,54 +1379,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
+          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.5813</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -1442,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786127300</t>
+          <t>1786130175</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>40.939394</t>
+          <t>1.72043</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,7 +1483,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
+          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1507,31 +1491,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>133.51</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1554,7 +1530,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786127185</t>
+          <t>1786129855</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7.548872</t>
+          <t>193.492754</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1587,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
+          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1626,22 +1602,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.22719</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1666,7 +1642,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1696,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786127185</t>
+          <t>1786129674</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>4.325359</t>
+          <t>3.197889</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,23 +1699,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
+          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.1825</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1747,7 +1727,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1755,27 +1739,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1800,17 +1784,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786126618</t>
+          <t>1786129636</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>117.808219</t>
+          <t>13.029316</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,7 +1811,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
+          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1835,31 +1819,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1882,7 +1858,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1888,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786124013</t>
+          <t>1786129590</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1898,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>16.761905</t>
+          <t>22.150289</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,23 +1915,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
+          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>4.16999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.6787</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786123790</t>
+          <t>1786129160</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2002,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>56.382353</t>
+          <t>6.143632</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,39 +2019,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
+          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>25.5377</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2098,7 +2066,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2128,7 +2096,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786123308</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2106,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>6.247619</t>
+          <t>48.527696</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,39 +2123,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
+          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>20.42793</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Casa Pia</t>
-        </is>
-      </c>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2195,27 +2155,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2240,17 +2200,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786114912</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>7.363636</t>
+          <t>38.817919</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2267,28 +2227,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
+          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>64.99</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2314,7 +2274,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2344,7 +2304,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786114872</t>
+          <t>1786128768</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2354,7 +2314,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>104.192385</t>
+          <t>9.691211</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,54 +2331,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
+          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -2426,7 +2378,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2456,7 +2408,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786112735</t>
+          <t>1786128742</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2466,7 +2418,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3.088803</t>
+          <t>46.645012</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,12 +2435,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
+          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2498,22 +2450,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>10.60893</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril 0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2538,7 +2490,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2568,7 +2520,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786090860</t>
+          <t>1786128656</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2578,7 +2530,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>25.350211</t>
+          <t>21.650878</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2595,12 +2547,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
+          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2615,34 +2567,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -2650,7 +2602,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2680,7 +2632,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786089858</t>
+          <t>1786128630</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2690,7 +2642,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>11.019284</t>
+          <t>6.791171</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,31 +2659,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
+          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.07999</t>
+          <t>64.79</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2739,27 +2699,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2784,17 +2744,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786085661</t>
+          <t>1786128598</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>4.93786</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,12 +2771,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
+          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2826,12 +2786,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2841,7 +2801,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2851,27 +2811,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2896,17 +2856,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786082857</t>
+          <t>1786127300</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>86.956522</t>
+          <t>40.939394</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,12 +2883,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2938,22 +2898,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2963,27 +2923,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3008,17 +2968,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>7.548872</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3035,12 +2995,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3050,22 +3010,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3075,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3120,17 +3080,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>4.325359</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,23 +3107,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.1825</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3179,27 +3139,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3224,17 +3184,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786126618</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>117.808219</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3251,31 +3211,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3283,27 +3251,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3328,17 +3296,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786124013</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>16.761905</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3355,23 +3323,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>38.34</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3387,27 +3355,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3432,17 +3400,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786123790</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>56.382353</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3459,31 +3427,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3491,27 +3467,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3536,17 +3512,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786123308</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>6.247619</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3563,23 +3539,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3587,7 +3567,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3595,27 +3579,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3640,17 +3624,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786114912</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>7.363636</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3667,23 +3651,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>64.99</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3699,27 +3683,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3744,17 +3728,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786114872</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>104.192385</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,23 +3755,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3795,7 +3783,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3803,27 +3795,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3848,17 +3840,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786112735</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>3.088803</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3875,23 +3867,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3899,7 +3895,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3907,27 +3907,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3952,17 +3952,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786090860</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>25.350211</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,31 +3979,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4011,27 +4019,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4056,17 +4064,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786089858</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>11.019284</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,23 +4091,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4115,27 +4123,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4160,17 +4168,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4187,23 +4195,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4211,7 +4223,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>FC Arouca</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4219,27 +4235,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4264,17 +4280,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4291,23 +4307,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4315,7 +4335,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4368,7 +4392,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4378,7 +4402,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4395,12 +4419,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4410,12 +4434,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4425,7 +4449,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4435,27 +4459,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4480,17 +4504,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4507,27 +4531,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4535,11 +4555,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4547,27 +4563,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4592,17 +4608,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,27 +4635,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4647,11 +4659,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4659,27 +4667,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4704,17 +4712,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,27 +4739,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4759,11 +4763,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4771,27 +4771,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4816,17 +4816,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,23 +4843,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4875,27 +4875,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4920,17 +4920,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,27 +4947,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4975,11 +4971,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4987,27 +4979,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5032,17 +5024,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5059,27 +5051,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5087,11 +5075,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5099,27 +5083,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5144,17 +5128,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5171,27 +5155,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5199,26 +5179,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>Estrela Amadora</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>Sporting Clube De Portugal CP</t>
@@ -5256,7 +5232,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5266,7 +5242,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5283,39 +5259,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5323,27 +5291,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5368,17 +5336,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5395,27 +5363,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5423,11 +5387,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5435,27 +5395,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5480,17 +5440,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5507,23 +5467,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5554,7 +5514,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5584,7 +5544,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5594,7 +5554,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5611,27 +5571,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5639,11 +5595,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5651,27 +5603,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5696,17 +5648,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5723,27 +5675,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5751,11 +5699,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5763,27 +5707,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5808,17 +5752,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5835,23 +5779,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5859,7 +5807,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5912,7 +5864,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5922,7 +5874,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5939,12 +5891,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5954,12 +5906,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5969,7 +5921,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5979,27 +5931,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6024,17 +5976,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6051,23 +6003,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6075,7 +6031,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6128,7 +6088,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6138,7 +6098,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6155,23 +6115,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6179,7 +6143,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6232,7 +6200,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6242,7 +6210,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6259,27 +6227,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6287,11 +6251,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6299,27 +6259,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6344,17 +6304,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6371,12 +6331,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6386,12 +6346,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6401,32 +6361,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6456,7 +6416,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6466,7 +6426,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6483,110 +6443,1534 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.2925</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1786048862</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>34.188034</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>19.0949</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.0662</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19516479</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1786045554</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1786217400</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>288.224906</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.4937</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1786045527</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>6.622785</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>10.12292</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.0362</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs Academico Viseu</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19551968</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1786045134</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1786303800</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>279.252966</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>20.58</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.2125</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19516479</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1786043934</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1786217400</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>96.847059</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.0513</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>FC Porto vs Alverca</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19516476</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1786025695</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1786294800</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.4125</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1786015629</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>19.345455</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1785807147</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.0525</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>FC Porto vs Alverca</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19516476</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1785805367</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1786294800</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>28.761905</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>70.81</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1785793268</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1785792146</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V70"/>
+  <dimension ref="A1:V74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
+          <t>0xd97957a2dbc75d4bbe2f8561247500721a9ccc599e0d1ddb1cb19dc3fc26b2c1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>91.02352</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4688</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x8c2bd7f367c91aaa67cce45975157c8fc230cd4f7dedf7ddf600e7b573e3ab54</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786135995</t>
+          <t>1786146808</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>194.183509</t>
+          <t>2.622951</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
+          <t>0x119ab2c3410b8d8f38cd160036d84db28ba2c49d7cebbdf58d09986906598c6e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>902.64812</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.5125</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786135994</t>
+          <t>1786146807</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1930.798118</t>
+          <t>3.570732</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
+          <t>0x0310cc4024f8c98d7c81dbc5746c8886ad1e2f2e8cb90d8cb5be5a6cfcc9c1a7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x07271e150ddc345829a0b5bbafef14c0cfe914219f2ef99cfebbd564cae832a9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786135800</t>
+          <t>1786146807</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>155.339806</t>
+          <t>3.755869</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,27 +843,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
+          <t>0x5bca4d812a5a27b447581f4377300e300e467043d3e15730460fad09ad91080c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.99999</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6488</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -871,11 +867,7 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -883,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786135027</t>
+          <t>1786138523</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>9.248539</t>
+          <t>7.357664</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,28 +947,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
+          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>91.02352</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2475</t>
+          <t>1.4688</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,7 +994,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786134086</t>
+          <t>1786135995</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>9.010101</t>
+          <t>194.183509</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,28 +1051,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
+          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>902.64812</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1091,27 +1083,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1128,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786132603</t>
+          <t>1786135994</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>134.757282</t>
+          <t>1930.798118</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,28 +1155,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
+          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1210,7 +1202,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1232,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786131718</t>
+          <t>1786135800</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1242,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>91.925466</t>
+          <t>155.339806</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,12 +1259,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
+          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1282,22 +1274,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>5.99999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2525</t>
+          <t>1.6488</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1322,7 +1314,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1352,7 +1344,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786130523</t>
+          <t>1786135027</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1354,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>552.475248</t>
+          <t>9.248539</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,28 +1371,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
+          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5813</t>
+          <t>1.2475</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1426,7 +1418,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1456,7 +1448,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786130175</t>
+          <t>1786134086</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.72043</t>
+          <t>9.010101</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,23 +1475,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
+          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>133.51</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1515,27 +1507,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1560,17 +1552,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786129855</t>
+          <t>1786132603</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>193.492754</t>
+          <t>134.757282</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,7 +1579,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
+          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1595,54 +1587,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.22719</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1672,7 +1656,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786129674</t>
+          <t>1786131718</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1682,7 +1666,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3.197889</t>
+          <t>91.925466</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,12 +1683,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
+          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1714,47 +1698,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.2525</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1784,7 +1768,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786129636</t>
+          <t>1786130523</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1794,7 +1778,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>13.029316</t>
+          <t>552.475248</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,28 +1795,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
+          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.5813</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1858,7 +1842,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1888,7 +1872,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786129590</t>
+          <t>1786130175</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1882,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>22.150289</t>
+          <t>1.72043</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,23 +1899,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
+          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.16999</t>
+          <t>133.51</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6787</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1992,7 +1976,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786129160</t>
+          <t>1786129855</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2002,7 +1986,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>6.143632</t>
+          <t>193.492754</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,36 +2003,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
+          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25.5377</t>
+          <t>1.22719</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
@@ -2066,7 +2058,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2096,7 +2088,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786128775</t>
+          <t>1786129674</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2106,7 +2098,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48.527696</t>
+          <t>3.197889</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,36 +2115,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
+          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.42793</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786128775</t>
+          <t>1786129636</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>38.817919</t>
+          <t>13.029316</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,28 +2227,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
+          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786128768</t>
+          <t>1786129590</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>9.691211</t>
+          <t>22.150289</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,28 +2331,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
+          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>4.16999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.6787</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786128742</t>
+          <t>1786129160</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>46.645012</t>
+          <t>6.143632</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,27 +2435,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
+          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10.60893</t>
+          <t>25.5377</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2463,11 +2459,7 @@
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Estoril 0</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2490,7 +2482,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2520,7 +2512,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786128656</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2530,7 +2522,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>21.650878</t>
+          <t>48.527696</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2547,39 +2539,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
+          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20.42793</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2602,7 +2586,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2632,7 +2616,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786128630</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2642,7 +2626,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>6.791171</t>
+          <t>38.817919</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2659,39 +2643,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
+          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>64.79</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2714,7 +2690,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2744,7 +2720,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786128598</t>
+          <t>1786128768</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2754,7 +2730,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>9.691211</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,54 +2747,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
+          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -2826,7 +2794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2856,7 +2824,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786127300</t>
+          <t>1786128742</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2866,7 +2834,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>40.939394</t>
+          <t>46.645012</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,12 +2851,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
+          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2898,22 +2866,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>10.60893</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Estoril 0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2938,7 +2906,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2968,7 +2936,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786127185</t>
+          <t>1786128656</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2978,7 +2946,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>7.548872</t>
+          <t>21.650878</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,12 +2963,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
+          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3010,22 +2978,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3050,7 +3018,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3080,7 +3048,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786127185</t>
+          <t>1786128630</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3090,7 +3058,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>4.325359</t>
+          <t>6.791171</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,31 +3075,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
+          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>64.79</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.1825</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3139,27 +3115,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3184,17 +3160,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786126618</t>
+          <t>1786128598</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>117.808219</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,7 +3187,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
+          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3226,22 +3202,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3266,7 +3242,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3296,7 +3272,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786124013</t>
+          <t>1786127300</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3306,7 +3282,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>16.761905</t>
+          <t>40.939394</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,7 +3299,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
+          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3331,23 +3307,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3370,7 +3354,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3400,7 +3384,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786123790</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3410,7 +3394,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>56.382353</t>
+          <t>7.548872</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3427,7 +3411,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
+          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3442,12 +3426,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3512,7 +3496,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786123308</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3522,7 +3506,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>6.247619</t>
+          <t>4.325359</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3539,27 +3523,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
+          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.1825</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3567,11 +3547,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Casa Pia</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3579,27 +3555,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
+          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3624,17 +3600,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786114912</t>
+          <t>1786126618</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>7.363636</t>
+          <t>117.808219</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3651,7 +3627,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
+          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3659,23 +3635,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>64.99</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3698,7 +3682,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3728,7 +3712,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786114872</t>
+          <t>1786124013</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3738,7 +3722,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>104.192385</t>
+          <t>16.761905</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3755,7 +3739,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
+          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3763,19 +3747,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38.34</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3783,26 +3763,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -3840,7 +3816,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786112735</t>
+          <t>1786123790</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3850,7 +3826,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>3.088803</t>
+          <t>56.382353</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,12 +3843,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
+          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3882,22 +3858,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3922,7 +3898,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3952,7 +3928,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786090860</t>
+          <t>1786123308</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3962,7 +3938,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>25.350211</t>
+          <t>6.247619</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,12 +3955,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
+          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3994,52 +3970,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4064,17 +4040,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786089858</t>
+          <t>1786114912</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11.019284</t>
+          <t>7.363636</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4091,18 +4067,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
+          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3.07999</t>
+          <t>64.99</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4123,27 +4099,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4168,17 +4144,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786085661</t>
+          <t>1786114872</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>4.93786</t>
+          <t>104.192385</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4195,12 +4171,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
+          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4210,12 +4186,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4225,7 +4201,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4235,27 +4211,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4280,17 +4256,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786082857</t>
+          <t>1786112735</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>86.956522</t>
+          <t>3.088803</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,12 +4283,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4322,12 +4298,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4337,7 +4313,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4347,27 +4323,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4392,17 +4368,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786090860</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>25.350211</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,12 +4395,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4434,22 +4410,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4459,27 +4435,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4504,17 +4480,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786089858</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>11.019284</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4531,23 +4507,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4563,27 +4539,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4608,17 +4584,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4635,23 +4611,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4659,7 +4639,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>FC Arouca</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4667,27 +4651,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4712,17 +4696,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4739,23 +4723,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4763,7 +4751,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4816,7 +4808,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4826,7 +4818,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,23 +4835,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4867,7 +4863,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,7 +4947,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5051,7 +5051,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5259,7 +5259,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5467,7 +5467,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5571,7 +5571,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5675,7 +5675,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5686,7 +5686,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5779,27 +5779,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5807,11 +5803,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5819,27 +5811,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5864,17 +5856,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5891,27 +5883,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5919,11 +5907,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5931,27 +5915,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5976,17 +5960,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6003,27 +5987,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6031,11 +6011,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6043,27 +6019,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6088,17 +6064,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6115,27 +6091,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6143,11 +6115,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6155,27 +6123,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6200,17 +6168,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6227,23 +6195,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6251,7 +6223,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6259,27 +6235,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6304,17 +6280,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6331,12 +6307,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6346,12 +6322,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6361,7 +6337,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6371,27 +6347,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6416,17 +6392,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6443,7 +6419,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6458,12 +6434,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6473,7 +6449,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6498,7 +6474,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6528,7 +6504,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6538,7 +6514,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6555,12 +6531,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6570,12 +6546,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6585,7 +6561,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6595,27 +6571,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6640,17 +6616,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6667,39 +6643,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6707,27 +6675,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6752,17 +6720,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6779,12 +6747,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6794,12 +6762,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6809,7 +6777,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6819,27 +6787,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6864,17 +6832,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6891,23 +6859,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6915,7 +6887,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6923,27 +6899,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6968,17 +6944,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6995,12 +6971,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7010,12 +6986,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7025,7 +7001,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7035,27 +7011,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7080,17 +7056,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7107,12 +7083,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7122,47 +7098,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7192,7 +7168,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7202,7 +7178,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7219,23 +7195,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7243,7 +7223,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7251,27 +7235,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7296,17 +7280,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7323,27 +7307,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7351,11 +7331,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7363,27 +7339,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7408,17 +7384,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7435,23 +7411,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7459,7 +7439,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7467,27 +7451,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7512,17 +7496,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7539,23 +7523,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7563,7 +7551,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7586,7 +7578,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7616,7 +7608,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7626,7 +7618,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7643,27 +7635,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7671,11 +7659,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7698,7 +7682,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7728,7 +7712,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7738,7 +7722,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7755,12 +7739,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7770,12 +7754,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7785,7 +7769,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7795,27 +7779,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7840,17 +7824,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7867,110 +7851,542 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>70.81</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1785793268</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1785792146</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="V74" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V74"/>
+  <dimension ref="A1:V75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd97957a2dbc75d4bbe2f8561247500721a9ccc599e0d1ddb1cb19dc3fc26b2c1</t>
+          <t>0x9d125073ec3f524cb81634bff9543957acd51d142414ae50799b56772cacc2b5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.1725</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x8c2bd7f367c91aaa67cce45975157c8fc230cd4f7dedf7ddf600e7b573e3ab54</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786146808</t>
+          <t>1786161908</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.622951</t>
+          <t>12.985507</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x119ab2c3410b8d8f38cd160036d84db28ba2c49d7cebbdf58d09986906598c6e</t>
+          <t>0xd97957a2dbc75d4bbe2f8561247500721a9ccc599e0d1ddb1cb19dc3fc26b2c1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,12 +646,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5125</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
+          <t>0x8c2bd7f367c91aaa67cce45975157c8fc230cd4f7dedf7ddf600e7b573e3ab54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786146807</t>
+          <t>1786146808</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.570732</t>
+          <t>2.622951</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x0310cc4024f8c98d7c81dbc5746c8886ad1e2f2e8cb90d8cb5be5a6cfcc9c1a7</t>
+          <t>0x119ab2c3410b8d8f38cd160036d84db28ba2c49d7cebbdf58d09986906598c6e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,17 +750,17 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5125</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x07271e150ddc345829a0b5bbafef14c0cfe914219f2ef99cfebbd564cae832a9</t>
+          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.755869</t>
+          <t>3.570732</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,23 +843,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x5bca4d812a5a27b447581f4377300e300e467043d3e15730460fad09ad91080c</t>
+          <t>0x0310cc4024f8c98d7c81dbc5746c8886ad1e2f2e8cb90d8cb5be5a6cfcc9c1a7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
+          <t>0x07271e150ddc345829a0b5bbafef14c0cfe914219f2ef99cfebbd564cae832a9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786138523</t>
+          <t>1786146807</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>7.357664</t>
+          <t>3.755869</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +947,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
+          <t>0x5bca4d812a5a27b447581f4377300e300e467043d3e15730460fad09ad91080c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>91.02352</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4688</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -979,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786135995</t>
+          <t>1786138523</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>194.183509</t>
+          <t>7.357664</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
+          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1062,12 +1062,12 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>902.64812</t>
+          <t>91.02352</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.4688</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786135994</t>
+          <t>1786135995</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1930.798118</t>
+          <t>194.183509</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,28 +1155,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
+          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>902.64812</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786135800</t>
+          <t>1786135994</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>155.339806</t>
+          <t>1930.798118</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,39 +1259,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
+          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.99999</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.6488</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1314,7 +1306,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1344,7 +1336,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786135027</t>
+          <t>1786135800</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1346,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>9.248539</t>
+          <t>155.339806</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,23 +1363,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
+          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.99999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2475</t>
+          <t>1.6488</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1395,7 +1391,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786134086</t>
+          <t>1786135027</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>9.010101</t>
+          <t>9.248539</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,28 +1475,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
+          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.2475</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1507,27 +1507,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786132603</t>
+          <t>1786134086</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>134.757282</t>
+          <t>9.010101</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,28 +1579,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
+          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1611,27 +1611,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
+          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786131718</t>
+          <t>1786132603</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>91.925466</t>
+          <t>134.757282</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,39 +1683,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
+          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2525</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1738,7 +1730,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1768,7 +1760,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786130523</t>
+          <t>1786131718</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1778,7 +1770,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>552.475248</t>
+          <t>91.925466</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,36 +1787,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
+          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5813</t>
+          <t>1.2525</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786130175</t>
+          <t>1786130523</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.72043</t>
+          <t>552.475248</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,28 +1899,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
+          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>133.51</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.5813</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786129855</t>
+          <t>1786130175</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>193.492754</t>
+          <t>1.72043</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
+          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2011,19 +2011,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.22719</t>
+          <t>133.51</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2031,34 +2027,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2088,7 +2080,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786129674</t>
+          <t>1786129855</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2098,7 +2090,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3.197889</t>
+          <t>193.492754</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,12 +2107,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
+          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2130,7 +2122,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.22719</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2200,7 +2192,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786129636</t>
+          <t>1786129674</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2210,7 +2202,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>13.029316</t>
+          <t>3.197889</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,31 +2219,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
+          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786129590</t>
+          <t>1786129636</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>22.150289</t>
+          <t>13.029316</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,28 +2331,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
+          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.16999</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.6787</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786129160</t>
+          <t>1786129590</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>6.143632</t>
+          <t>22.150289</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,28 +2435,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
+          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.5377</t>
+          <t>4.16999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.6787</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786128775</t>
+          <t>1786129160</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.527696</t>
+          <t>6.143632</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
+          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2550,7 +2550,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20.42793</t>
+          <t>25.5377</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>38.817919</t>
+          <t>48.527696</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,18 +2643,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
+          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>20.42793</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786128768</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>9.691211</t>
+          <t>38.817919</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
+          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,17 +2758,17 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786128742</t>
+          <t>1786128768</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>46.645012</t>
+          <t>9.691211</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2851,44 +2851,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
+          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.60893</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Estoril 0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
@@ -2906,7 +2898,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2936,7 +2928,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786128656</t>
+          <t>1786128742</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2946,7 +2938,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>21.650878</t>
+          <t>46.645012</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2963,12 +2955,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
+          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2978,22 +2970,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10.60893</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Estoril 0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3018,7 +3010,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3048,7 +3040,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786128630</t>
+          <t>1786128656</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3058,7 +3050,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>6.791171</t>
+          <t>21.650878</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3075,12 +3067,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
+          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3090,7 +3082,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>64.79</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3160,7 +3152,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786128598</t>
+          <t>1786128630</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3170,7 +3162,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>6.791171</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3187,12 +3179,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
+          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3202,39 +3194,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>64.79</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -3242,7 +3234,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3272,7 +3264,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786127300</t>
+          <t>1786128598</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3282,7 +3274,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>40.939394</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3299,7 +3291,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
+          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3314,22 +3306,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3354,7 +3346,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3384,7 +3376,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786127185</t>
+          <t>1786127300</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3394,7 +3386,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>7.548872</t>
+          <t>40.939394</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3411,7 +3403,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
+          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3426,22 +3418,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3466,7 +3458,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3506,7 +3498,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4.325359</t>
+          <t>7.548872</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3523,31 +3515,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
+          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.1825</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3555,27 +3555,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3600,17 +3600,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786126618</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>117.808219</t>
+          <t>4.325359</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,39 +3627,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
+          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.1825</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3667,27 +3659,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3712,17 +3704,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786124013</t>
+          <t>1786126618</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>16.761905</t>
+          <t>117.808219</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3739,7 +3731,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
+          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3747,23 +3739,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786123790</t>
+          <t>1786124013</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>56.382353</t>
+          <t>16.761905</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3843,7 +3843,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
+          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3851,31 +3851,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>38.34</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3898,7 +3890,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3928,7 +3920,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786123308</t>
+          <t>1786123790</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3938,7 +3930,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>6.247619</t>
+          <t>56.382353</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,7 +3947,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
+          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3970,22 +3962,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3995,27 +3987,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4040,17 +4032,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786114912</t>
+          <t>1786123308</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>7.363636</t>
+          <t>6.247619</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4067,7 +4059,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
+          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4075,15 +4067,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>64.99</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4091,7 +4087,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4099,27 +4099,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786114872</t>
+          <t>1786114912</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>104.192385</t>
+          <t>7.363636</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,7 +4171,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
+          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4179,19 +4179,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>64.99</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4199,26 +4195,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -4226,7 +4218,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4256,7 +4248,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786112735</t>
+          <t>1786114872</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4266,7 +4258,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>3.088803</t>
+          <t>104.192385</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4283,12 +4275,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
+          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4298,12 +4290,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4313,7 +4305,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4338,7 +4330,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4368,7 +4360,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786090860</t>
+          <t>1786112735</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4378,7 +4370,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>25.350211</t>
+          <t>3.088803</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4395,12 +4387,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
+          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4410,39 +4402,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -4450,7 +4442,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4480,7 +4472,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786089858</t>
+          <t>1786090860</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4490,7 +4482,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11.019284</t>
+          <t>25.350211</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4507,31 +4499,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
+          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.07999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4539,27 +4539,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4584,17 +4584,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786085661</t>
+          <t>1786089858</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>4.93786</t>
+          <t>11.019284</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4611,27 +4611,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4639,11 +4635,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>FC Arouca</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4651,27 +4643,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4696,17 +4688,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786082857</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>86.956522</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,7 +4715,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4738,12 +4730,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4753,7 +4745,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4763,27 +4755,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4808,17 +4800,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,7 +4827,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4850,7 +4842,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4920,7 +4912,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4922,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,23 +4939,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4971,7 +4967,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,7 +5051,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5259,7 +5259,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5467,7 +5467,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5571,7 +5571,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5675,7 +5675,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5779,7 +5779,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5883,7 +5883,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5987,7 +5987,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6091,7 +6091,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6102,7 +6102,7 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6195,27 +6195,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6223,11 +6219,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6235,27 +6227,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6280,17 +6272,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6307,12 +6299,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6322,12 +6314,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6337,7 +6329,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6347,27 +6339,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6392,17 +6384,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6419,12 +6411,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6434,12 +6426,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6449,7 +6441,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6459,27 +6451,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6504,17 +6496,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6531,7 +6523,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6546,7 +6538,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6616,7 +6608,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6626,7 +6618,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6643,23 +6635,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6667,7 +6663,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6675,27 +6675,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6720,17 +6720,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6747,7 +6747,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6755,19 +6755,15 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6775,11 +6771,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6787,27 +6779,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6832,17 +6824,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6859,12 +6851,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6874,7 +6866,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6944,7 +6936,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6954,7 +6946,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6971,12 +6963,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6986,12 +6978,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7001,7 +6993,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7011,27 +7003,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7056,17 +7048,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7083,12 +7075,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7098,22 +7090,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7123,27 +7115,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7168,17 +7160,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7195,12 +7187,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7210,22 +7202,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7235,27 +7227,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7280,17 +7272,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7307,7 +7299,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7315,15 +7307,19 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7331,7 +7327,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7339,27 +7339,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7384,17 +7384,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7411,27 +7411,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7439,11 +7435,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7451,27 +7443,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7496,17 +7488,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7523,12 +7515,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7538,12 +7530,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7553,7 +7545,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7563,27 +7555,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7608,17 +7600,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7635,23 +7627,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7659,7 +7655,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7739,7 +7739,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7747,19 +7747,15 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7767,11 +7763,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7779,27 +7771,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7824,17 +7816,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7851,7 +7843,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7859,15 +7851,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7875,7 +7871,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7883,27 +7883,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7928,17 +7928,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7955,7 +7955,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7966,7 +7966,7 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8059,27 +8059,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8087,11 +8083,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -8114,7 +8106,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8144,7 +8136,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8154,7 +8146,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8171,12 +8163,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8186,12 +8178,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8201,32 +8193,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8256,7 +8248,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785703082</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8266,7 +8258,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>3.361345</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8283,110 +8275,222 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9d125073ec3f524cb81634bff9543957acd51d142414ae50799b56772cacc2b5</t>
+          <t>0x485b8bc1c25c4435ab81832174033d2b5706d64c4bba55f1d5a3579aeb3b5cb8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.875</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.1725</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
+          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786161908</t>
+          <t>1786165632</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>12.985507</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd97957a2dbc75d4bbe2f8561247500721a9ccc599e0d1ddb1cb19dc3fc26b2c1</t>
+          <t>0x9d125073ec3f524cb81634bff9543957acd51d142414ae50799b56772cacc2b5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.1725</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x8c2bd7f367c91aaa67cce45975157c8fc230cd4f7dedf7ddf600e7b573e3ab54</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786146808</t>
+          <t>1786161908</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.622951</t>
+          <t>12.985507</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x119ab2c3410b8d8f38cd160036d84db28ba2c49d7cebbdf58d09986906598c6e</t>
+          <t>0xd97957a2dbc75d4bbe2f8561247500721a9ccc599e0d1ddb1cb19dc3fc26b2c1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,12 +750,12 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5125</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -771,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
+          <t>0x8c2bd7f367c91aaa67cce45975157c8fc230cd4f7dedf7ddf600e7b573e3ab54</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786146807</t>
+          <t>1786146808</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.570732</t>
+          <t>2.622951</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x0310cc4024f8c98d7c81dbc5746c8886ad1e2f2e8cb90d8cb5be5a6cfcc9c1a7</t>
+          <t>0x119ab2c3410b8d8f38cd160036d84db28ba2c49d7cebbdf58d09986906598c6e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,17 +854,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x07271e150ddc345829a0b5bbafef14c0cfe914219f2ef99cfebbd564cae832a9</t>
+          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3.755869</t>
+          <t>3.570732</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,23 +947,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5bca4d812a5a27b447581f4377300e300e467043d3e15730460fad09ad91080c</t>
+          <t>0x0310cc4024f8c98d7c81dbc5746c8886ad1e2f2e8cb90d8cb5be5a6cfcc9c1a7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -979,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
+          <t>0x07271e150ddc345829a0b5bbafef14c0cfe914219f2ef99cfebbd564cae832a9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786138523</t>
+          <t>1786146807</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7.357664</t>
+          <t>3.755869</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,28 +1051,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
+          <t>0x5bca4d812a5a27b447581f4377300e300e467043d3e15730460fad09ad91080c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>91.02352</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4688</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1083,27 +1083,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786135995</t>
+          <t>1786138523</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>194.183509</t>
+          <t>7.357664</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
+          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1166,12 +1166,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>902.64812</t>
+          <t>91.02352</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.4688</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786135994</t>
+          <t>1786135995</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1930.798118</t>
+          <t>194.183509</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,28 +1259,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
+          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>902.64812</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786135800</t>
+          <t>1786135994</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>155.339806</t>
+          <t>1930.798118</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1363,39 +1363,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
+          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.99999</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6488</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1418,7 +1410,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1448,7 +1440,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786135027</t>
+          <t>1786135800</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1450,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>9.248539</t>
+          <t>155.339806</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,23 +1467,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
+          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>5.99999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2475</t>
+          <t>1.6488</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1499,7 +1495,11 @@
           <t>Under/Over (1.5)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786134086</t>
+          <t>1786135027</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>9.010101</t>
+          <t>9.248539</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,28 +1579,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
+          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.2475</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1611,27 +1611,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786132603</t>
+          <t>1786134086</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>134.757282</t>
+          <t>9.010101</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,28 +1683,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
+          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1715,27 +1715,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
+          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786131718</t>
+          <t>1786132603</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>91.925466</t>
+          <t>134.757282</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,39 +1787,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
+          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2525</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1842,7 +1834,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1872,7 +1864,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786130523</t>
+          <t>1786131718</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1882,7 +1874,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>552.475248</t>
+          <t>91.925466</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,36 +1891,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
+          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5813</t>
+          <t>1.2525</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786130175</t>
+          <t>1786130523</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.72043</t>
+          <t>552.475248</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,28 +2003,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
+          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>133.51</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.5813</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786129855</t>
+          <t>1786130175</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>193.492754</t>
+          <t>1.72043</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,7 +2107,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
+          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2115,19 +2115,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.22719</t>
+          <t>133.51</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2135,34 +2131,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2192,7 +2184,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786129674</t>
+          <t>1786129855</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2202,7 +2194,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3.197889</t>
+          <t>193.492754</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2219,12 +2211,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
+          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2234,7 +2226,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.22719</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2304,7 +2296,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786129636</t>
+          <t>1786129674</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2314,7 +2306,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13.029316</t>
+          <t>3.197889</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,31 +2323,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
+          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786129590</t>
+          <t>1786129636</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>22.150289</t>
+          <t>13.029316</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,28 +2435,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
+          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.16999</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.6787</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786129160</t>
+          <t>1786129590</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>6.143632</t>
+          <t>22.150289</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,28 +2539,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
+          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.5377</t>
+          <t>4.16999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.6787</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786128775</t>
+          <t>1786129160</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.527696</t>
+          <t>6.143632</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,7 +2643,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
+          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2654,7 +2654,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20.42793</t>
+          <t>25.5377</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>38.817919</t>
+          <t>48.527696</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,18 +2747,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
+          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>20.42793</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786128768</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>9.691211</t>
+          <t>38.817919</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2851,7 +2851,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
+          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2862,17 +2862,17 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786128742</t>
+          <t>1786128768</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>46.645012</t>
+          <t>9.691211</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2955,44 +2955,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
+          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.60893</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Estoril 0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
@@ -3010,7 +3002,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3040,7 +3032,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786128656</t>
+          <t>1786128742</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3050,7 +3042,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>21.650878</t>
+          <t>46.645012</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3067,12 +3059,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
+          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3082,22 +3074,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10.60893</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Estoril 0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3122,7 +3114,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3152,7 +3144,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786128630</t>
+          <t>1786128656</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3162,7 +3154,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>6.791171</t>
+          <t>21.650878</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3179,12 +3171,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
+          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3194,7 +3186,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>64.79</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3264,7 +3256,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786128598</t>
+          <t>1786128630</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3274,7 +3266,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>6.791171</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3291,12 +3283,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
+          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3306,39 +3298,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>64.79</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -3346,7 +3338,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3376,7 +3368,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786127300</t>
+          <t>1786128598</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3386,7 +3378,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>40.939394</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3403,7 +3395,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
+          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3418,22 +3410,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3458,7 +3450,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3488,7 +3480,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786127185</t>
+          <t>1786127300</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3498,7 +3490,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>7.548872</t>
+          <t>40.939394</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3515,7 +3507,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
+          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3530,22 +3522,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3570,7 +3562,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3610,7 +3602,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>4.325359</t>
+          <t>7.548872</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,31 +3619,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
+          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.1825</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3659,27 +3659,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3704,17 +3704,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786126618</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>117.808219</t>
+          <t>4.325359</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3731,39 +3731,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
+          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.1825</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3771,27 +3763,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3816,17 +3808,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786124013</t>
+          <t>1786126618</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>16.761905</t>
+          <t>117.808219</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3843,7 +3835,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
+          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3851,23 +3843,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786123790</t>
+          <t>1786124013</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>56.382353</t>
+          <t>16.761905</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3947,7 +3947,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
+          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3955,31 +3955,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>38.34</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4002,7 +3994,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4032,7 +4024,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786123308</t>
+          <t>1786123790</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4042,7 +4034,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>6.247619</t>
+          <t>56.382353</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4059,7 +4051,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
+          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4074,22 +4066,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4099,27 +4091,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4144,17 +4136,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786114912</t>
+          <t>1786123308</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>7.363636</t>
+          <t>6.247619</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,7 +4163,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
+          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4179,15 +4171,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>64.99</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4195,7 +4191,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4203,27 +4203,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786114872</t>
+          <t>1786114912</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>104.192385</t>
+          <t>7.363636</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4275,7 +4275,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
+          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4283,19 +4283,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>64.99</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4303,26 +4299,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -4330,7 +4322,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4360,7 +4352,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786112735</t>
+          <t>1786114872</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4370,7 +4362,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>3.088803</t>
+          <t>104.192385</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4387,12 +4379,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
+          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4402,12 +4394,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4417,7 +4409,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4442,7 +4434,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4472,7 +4464,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786090860</t>
+          <t>1786112735</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4482,7 +4474,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>25.350211</t>
+          <t>3.088803</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4499,12 +4491,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
+          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4514,39 +4506,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -4554,7 +4546,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4584,7 +4576,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786089858</t>
+          <t>1786090860</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4594,7 +4586,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>11.019284</t>
+          <t>25.350211</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4611,31 +4603,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
+          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.07999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4643,27 +4643,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786085661</t>
+          <t>1786089858</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>4.93786</t>
+          <t>11.019284</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4715,27 +4715,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4743,11 +4739,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>FC Arouca</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4755,27 +4747,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4800,17 +4792,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786082857</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>86.956522</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4827,7 +4819,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4842,12 +4834,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4857,7 +4849,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4867,27 +4859,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4912,17 +4904,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,7 +4931,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4954,7 +4946,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5024,7 +5016,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5026,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,23 +5043,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5075,7 +5071,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5259,7 +5259,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5467,7 +5467,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5571,7 +5571,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5675,7 +5675,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5779,7 +5779,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5883,7 +5883,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5987,7 +5987,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6091,7 +6091,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6195,7 +6195,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6206,7 +6206,7 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6299,27 +6299,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6327,11 +6323,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6339,27 +6331,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6384,17 +6376,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6411,12 +6403,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6426,12 +6418,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6441,7 +6433,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6451,27 +6443,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6496,17 +6488,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6523,12 +6515,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6538,12 +6530,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6553,7 +6545,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6563,27 +6555,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6608,17 +6600,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6635,7 +6627,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6650,7 +6642,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6720,7 +6712,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6730,7 +6722,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6747,23 +6739,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6771,7 +6767,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6779,27 +6779,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6824,17 +6824,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6851,7 +6851,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6859,19 +6859,15 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6879,11 +6875,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6891,27 +6883,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6936,17 +6928,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6963,12 +6955,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6978,7 +6970,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7048,7 +7040,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7058,7 +7050,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7075,12 +7067,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7090,12 +7082,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7105,7 +7097,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7115,27 +7107,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7160,17 +7152,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7187,12 +7179,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7202,22 +7194,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7227,27 +7219,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7272,17 +7264,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7299,12 +7291,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7314,22 +7306,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7339,27 +7331,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7384,17 +7376,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7411,7 +7403,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7419,15 +7411,19 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7435,7 +7431,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7443,27 +7443,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7488,17 +7488,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7515,27 +7515,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7543,11 +7539,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7555,27 +7547,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7600,17 +7592,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7627,12 +7619,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7642,12 +7634,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7657,7 +7649,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7667,27 +7659,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7712,17 +7704,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7739,23 +7731,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7763,7 +7759,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7843,7 +7843,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7851,19 +7851,15 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7871,11 +7867,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7883,27 +7875,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7928,17 +7920,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7955,7 +7947,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7963,15 +7955,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7979,7 +7975,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7987,27 +7987,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8032,17 +8032,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8059,7 +8059,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8070,7 +8070,7 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8163,27 +8163,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8191,11 +8187,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -8218,7 +8210,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8248,7 +8240,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785792146</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8258,7 +8250,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>1.383562</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8275,12 +8267,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8290,12 +8282,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8305,32 +8297,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8360,7 +8352,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785703082</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8370,7 +8362,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>3.361345</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8387,110 +8379,222 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V76"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x485b8bc1c25c4435ab81832174033d2b5706d64c4bba55f1d5a3579aeb3b5cb8</t>
+          <t>0x11704d547b1815563cbcfd427f86f694149a2fb294772bc435a64f032e6f9535</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.875</t>
+          <t>11.94789</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786165632</t>
+          <t>1786174340</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>23.717896</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x9d125073ec3f524cb81634bff9543957acd51d142414ae50799b56772cacc2b5</t>
+          <t>0xb33331a7c5dd3fa9ae4b279afdd5bd3f6795da10e428eef1cd4da6555f3d6f53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,12 +646,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.1725</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786161908</t>
+          <t>1786174324</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>12.985507</t>
+          <t>5.555556</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,31 +739,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xd97957a2dbc75d4bbe2f8561247500721a9ccc599e0d1ddb1cb19dc3fc26b2c1</t>
+          <t>0xbcfad4be403d17328f68e33c671150e1aacf19949b68ac560e5aef53c0d366c5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Asian Handicap (2)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Estrela Amadora +2</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -786,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x8c2bd7f367c91aaa67cce45975157c8fc230cd4f7dedf7ddf600e7b573e3ab54</t>
+          <t>0x3f96edde1005ba9d9c39379e32194aca486d726c35b7575193b798ad688ec098</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786146808</t>
+          <t>1786172968</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.622951</t>
+          <t>62.914661</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,23 +851,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x119ab2c3410b8d8f38cd160036d84db28ba2c49d7cebbdf58d09986906598c6e</t>
+          <t>0x485b8bc1c25c4435ab81832174033d2b5706d64c4bba55f1d5a3579aeb3b5cb8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>12.875</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5125</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -920,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786146807</t>
+          <t>1786165632</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3.570732</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,23 +955,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x0310cc4024f8c98d7c81dbc5746c8886ad1e2f2e8cb90d8cb5be5a6cfcc9c1a7</t>
+          <t>0x9d125073ec3f524cb81634bff9543957acd51d142414ae50799b56772cacc2b5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.1725</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -979,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x07271e150ddc345829a0b5bbafef14c0cfe914219f2ef99cfebbd564cae832a9</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786146807</t>
+          <t>1786161908</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.755869</t>
+          <t>12.985507</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,28 +1059,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5bca4d812a5a27b447581f4377300e300e467043d3e15730460fad09ad91080c</t>
+          <t>0xd97957a2dbc75d4bbe2f8561247500721a9ccc599e0d1ddb1cb19dc3fc26b2c1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1098,7 +1106,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
+          <t>0x8c2bd7f367c91aaa67cce45975157c8fc230cd4f7dedf7ddf600e7b573e3ab54</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1128,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786138523</t>
+          <t>1786146808</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1138,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7.357664</t>
+          <t>2.622951</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,28 +1163,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
+          <t>0x119ab2c3410b8d8f38cd160036d84db28ba2c49d7cebbdf58d09986906598c6e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>91.02352</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4688</t>
+          <t>1.5125</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1187,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1232,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786135995</t>
+          <t>1786146807</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>194.183509</t>
+          <t>3.570732</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,28 +1267,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
+          <t>0x0310cc4024f8c98d7c81dbc5746c8886ad1e2f2e8cb90d8cb5be5a6cfcc9c1a7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>902.64812</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1291,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x07271e150ddc345829a0b5bbafef14c0cfe914219f2ef99cfebbd564cae832a9</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1336,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786135994</t>
+          <t>1786146807</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1930.798118</t>
+          <t>3.755869</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1363,28 +1371,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
+          <t>0x5bca4d812a5a27b447581f4377300e300e467043d3e15730460fad09ad91080c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1395,27 +1403,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1440,17 +1448,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786135800</t>
+          <t>1786138523</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>155.339806</t>
+          <t>7.357664</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1467,39 +1475,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
+          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.99999</t>
+          <t>91.02352</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6488</t>
+          <t>1.4688</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786135027</t>
+          <t>1786135995</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>9.248539</t>
+          <t>194.183509</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,28 +1579,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
+          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>902.64812</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2475</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786134086</t>
+          <t>1786135994</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>9.010101</t>
+          <t>1930.798118</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,23 +1683,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
+          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1715,27 +1715,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786132603</t>
+          <t>1786135800</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>134.757282</t>
+          <t>155.339806</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,31 +1787,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
+          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>5.99999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.6488</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1834,7 +1842,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1864,7 +1872,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786131718</t>
+          <t>1786135027</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1874,7 +1882,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>91.925466</t>
+          <t>9.248539</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1891,39 +1899,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
+          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2525</t>
+          <t>1.2475</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786130523</t>
+          <t>1786134086</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>552.475248</t>
+          <t>9.010101</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,28 +2003,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
+          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5813</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2035,27 +2035,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786130175</t>
+          <t>1786132603</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.72043</t>
+          <t>134.757282</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,7 +2107,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
+          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2118,17 +2118,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>133.51</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786129855</t>
+          <t>1786131718</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>193.492754</t>
+          <t>91.925466</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2211,12 +2211,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
+          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2226,47 +2226,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.22719</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.2525</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786129674</t>
+          <t>1786130523</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3.197889</t>
+          <t>552.475248</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,62 +2323,54 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
+          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.5813</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2408,7 +2400,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786129636</t>
+          <t>1786130175</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2410,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13.029316</t>
+          <t>1.72043</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,7 +2427,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
+          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2446,17 +2438,17 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>133.51</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2482,7 +2474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2512,7 +2504,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786129590</t>
+          <t>1786129855</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2522,7 +2514,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>22.150289</t>
+          <t>193.492754</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,23 +2531,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
+          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.16999</t>
+          <t>1.22719</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6787</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2563,7 +2559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786129160</t>
+          <t>1786129674</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>6.143632</t>
+          <t>3.197889</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,36 +2643,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
+          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25.5377</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
@@ -2690,7 +2698,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2720,7 +2728,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786128775</t>
+          <t>1786129636</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2738,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>48.527696</t>
+          <t>13.029316</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,28 +2755,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
+          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20.42793</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2794,7 +2802,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2824,7 +2832,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786128775</t>
+          <t>1786129590</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2834,7 +2842,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>38.817919</t>
+          <t>22.150289</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2851,28 +2859,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
+          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.16999</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.6787</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2898,7 +2906,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2928,7 +2936,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786128768</t>
+          <t>1786129160</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2938,7 +2946,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>9.691211</t>
+          <t>6.143632</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2955,28 +2963,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
+          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>25.5377</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3002,7 +3010,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3032,7 +3040,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786128742</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3042,7 +3050,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>46.645012</t>
+          <t>48.527696</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3059,27 +3067,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
+          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10.60893</t>
+          <t>20.42793</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3087,11 +3091,7 @@
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Estoril 0</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786128656</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>21.650878</t>
+          <t>38.817919</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3171,39 +3171,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
+          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3226,7 +3218,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3256,7 +3248,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786128630</t>
+          <t>1786128768</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3266,7 +3258,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>6.791171</t>
+          <t>9.691211</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3283,39 +3275,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
+          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>64.79</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3338,7 +3322,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3368,7 +3352,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786128598</t>
+          <t>1786128742</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3378,7 +3362,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>46.645012</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3395,12 +3379,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
+          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3410,39 +3394,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>10.60893</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>Estoril 0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -3450,7 +3434,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3480,7 +3464,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786127300</t>
+          <t>1786128656</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3490,7 +3474,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>40.939394</t>
+          <t>21.650878</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3507,12 +3491,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
+          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3522,22 +3506,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3562,7 +3546,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3592,7 +3576,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786127185</t>
+          <t>1786128630</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3602,7 +3586,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>7.548872</t>
+          <t>6.791171</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3619,12 +3603,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
+          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3634,22 +3618,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>64.79</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3674,7 +3658,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3704,7 +3688,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786127185</t>
+          <t>1786128598</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3714,7 +3698,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>4.325359</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3731,23 +3715,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
+          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.1825</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3755,7 +3743,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3763,27 +3755,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3808,17 +3800,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786126618</t>
+          <t>1786127300</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>117.808219</t>
+          <t>40.939394</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3835,7 +3827,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
+          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3850,22 +3842,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3890,7 +3882,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3920,7 +3912,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786124013</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3930,7 +3922,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>16.761905</t>
+          <t>7.548872</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3947,7 +3939,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
+          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3955,23 +3947,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786123790</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>56.382353</t>
+          <t>4.325359</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4051,39 +4051,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
+          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.1825</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4091,27 +4083,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4136,17 +4128,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786123308</t>
+          <t>1786126618</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>6.247619</t>
+          <t>117.808219</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4163,7 +4155,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
+          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4178,22 +4170,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4203,27 +4195,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4248,17 +4240,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786114912</t>
+          <t>1786124013</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>7.363636</t>
+          <t>16.761905</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4275,7 +4267,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
+          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4286,12 +4278,12 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>64.99</t>
+          <t>38.34</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4322,7 +4314,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4352,7 +4344,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786114872</t>
+          <t>1786123790</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4362,7 +4354,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>104.192385</t>
+          <t>56.382353</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4379,7 +4371,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
+          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4394,39 +4386,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -4434,7 +4426,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4464,7 +4456,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786112735</t>
+          <t>1786123308</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4474,7 +4466,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>3.088803</t>
+          <t>6.247619</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4491,12 +4483,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
+          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4506,12 +4498,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4521,7 +4513,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4531,27 +4523,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4576,17 +4568,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786090860</t>
+          <t>1786114912</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>25.350211</t>
+          <t>7.363636</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4603,54 +4595,46 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
+          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>64.99</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -4658,7 +4642,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4688,7 +4672,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786089858</t>
+          <t>1786114872</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4698,7 +4682,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>11.019284</t>
+          <t>104.192385</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4715,23 +4699,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
+          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.07999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4739,7 +4727,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4747,27 +4739,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4792,17 +4784,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786085661</t>
+          <t>1786112735</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>4.93786</t>
+          <t>3.088803</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4819,12 +4811,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
+          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4834,12 +4826,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4849,7 +4841,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4859,27 +4851,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4904,17 +4896,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786082857</t>
+          <t>1786090860</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>86.956522</t>
+          <t>25.350211</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4931,12 +4923,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4946,22 +4938,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4971,27 +4963,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5016,17 +5008,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786089858</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>11.019284</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5043,27 +5035,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5071,11 +5059,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5083,27 +5067,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5128,17 +5112,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,23 +5139,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5179,7 +5167,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>FC Arouca</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5187,27 +5179,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5232,17 +5224,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5259,23 +5251,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5283,7 +5279,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5363,23 +5363,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5387,7 +5391,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5440,7 +5448,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5450,7 +5458,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5467,7 +5475,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5544,7 +5552,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5571,7 +5579,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5648,7 +5656,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5675,7 +5683,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5752,7 +5760,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5779,7 +5787,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5856,7 +5864,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5883,7 +5891,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5960,7 +5968,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5987,7 +5995,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6064,7 +6072,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6091,7 +6099,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6168,7 +6176,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6195,7 +6203,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6272,7 +6280,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6299,7 +6307,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6310,7 +6318,7 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6376,7 +6384,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6386,7 +6394,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6403,27 +6411,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6431,11 +6435,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6443,27 +6443,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6488,17 +6488,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6515,27 +6515,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6543,11 +6539,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6555,27 +6547,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6600,17 +6592,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6627,27 +6619,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6655,11 +6643,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6667,27 +6651,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6712,17 +6696,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6739,7 +6723,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6754,7 +6738,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6824,7 +6808,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6834,7 +6818,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6851,23 +6835,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6875,7 +6863,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6883,27 +6875,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6928,17 +6920,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6955,12 +6947,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6970,12 +6962,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6985,7 +6977,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7010,7 +7002,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7040,7 +7032,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7050,7 +7042,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7067,7 +7059,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7082,12 +7074,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7097,7 +7089,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7122,7 +7114,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7152,7 +7144,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7162,7 +7154,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7179,27 +7171,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7207,11 +7195,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7219,27 +7203,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7264,17 +7248,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7291,12 +7275,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7306,22 +7290,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7346,7 +7330,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7376,7 +7360,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7386,7 +7370,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7403,12 +7387,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7418,12 +7402,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7433,7 +7417,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7443,27 +7427,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7488,17 +7472,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7515,7 +7499,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7523,15 +7507,19 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>19.0949</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7539,7 +7527,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7562,7 +7554,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7592,7 +7584,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786045554</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7602,7 +7594,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>288.224906</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7619,12 +7611,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7634,22 +7626,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7659,27 +7651,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7704,17 +7696,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786045527</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.622785</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7731,12 +7723,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7746,12 +7738,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>10.12292</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7761,7 +7753,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7771,27 +7763,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7816,17 +7808,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786045134</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>279.252966</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7843,23 +7835,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7875,27 +7867,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7920,17 +7912,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786043934</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>96.847059</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7947,12 +7939,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7962,12 +7954,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.0513</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8032,7 +8024,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1786025695</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8042,7 +8034,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8059,23 +8051,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4125</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8083,7 +8079,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1786015629</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>19.345455</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8163,7 +8163,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1785807147</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8267,12 +8267,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.0525</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8307,27 +8307,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8352,17 +8352,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1785805367</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>28.761905</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8379,27 +8379,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>70.81</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8407,34 +8403,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8464,7 +8456,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1785793268</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8474,7 +8466,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8491,110 +8483,438 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1785792146</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="V79" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
+++ b/data/sxbet/ligas/Portugal Primeira Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V79"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x11704d547b1815563cbcfd427f86f694149a2fb294772bc435a64f032e6f9535</t>
+          <t>0xd9ee824ad88b3f15de31385821dab6546761b112162ec08f520a7971e8f2f073</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,23 +539,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.94789</t>
+          <t>12.70774</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Asian Handicap (1.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Estrela Amadora +1.5</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0x53c25314de39328675520662727242d4815f1c543d03ae4e1f7b19c8b74f370d</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786174340</t>
+          <t>1786190224</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>23.717896</t>
+          <t>27.037745</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xb33331a7c5dd3fa9ae4b279afdd5bd3f6795da10e428eef1cd4da6555f3d6f53</t>
+          <t>0x073b28de5aaf50091a5f02b22c70435457827ab3ffbf2b7bcc5e9cbd42515b1c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,23 +651,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.30999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.6075</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (2)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Estrela Amadora +2</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -682,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
+          <t>0x3f96edde1005ba9d9c39379e32194aca486d726c35b7575193b798ad688ec098</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786174324</t>
+          <t>1786190224</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>5.555556</t>
+          <t>3.802453</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,39 +755,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xbcfad4be403d17328f68e33c671150e1aacf19949b68ac560e5aef53c0d366c5</t>
+          <t>0x32a6701c12a066a43d8d5aed04e62a4d7242646abc0b15e8ea31858131603065</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>3.35854</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (2)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Estrela Amadora +2</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -794,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x3f96edde1005ba9d9c39379e32194aca486d726c35b7575193b798ad688ec098</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -824,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786172968</t>
+          <t>1786187436</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>62.914661</t>
+          <t>18.658556</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x485b8bc1c25c4435ab81832174033d2b5706d64c4bba55f1d5a3579aeb3b5cb8</t>
+          <t>0xd29c19660cd1a122e0ad1779b1b8fd787d68627679138922715e82d48c58a2f1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12.875</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.2275</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -883,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
+          <t>0xb4d500ac658083e0578f9852936a41941b654047817c4a49da0e07086f5a60b1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786165632</t>
+          <t>1786186733</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>4.835165</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,28 +963,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x9d125073ec3f524cb81634bff9543957acd51d142414ae50799b56772cacc2b5</t>
+          <t>0x040628d9219524e240f8297273de56933f66ce8a4195e4096b6acd7c436ea7c6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.1725</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
+          <t>0x53c25314de39328675520662727242d4815f1c543d03ae4e1f7b19c8b74f370d</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786161908</t>
+          <t>1786185061</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>12.985507</t>
+          <t>1.826484</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,28 +1067,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xd97957a2dbc75d4bbe2f8561247500721a9ccc599e0d1ddb1cb19dc3fc26b2c1</t>
+          <t>0xaf26f02efb12d85a965dcd2d25797e616f89f5d368eb547c865253831b390c37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.94595</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.3213</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1091,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x8c2bd7f367c91aaa67cce45975157c8fc230cd4f7dedf7ddf600e7b573e3ab54</t>
+          <t>0x6444aa437327ed02dd5aa9bc62539b2b75799d91ae7b30859c74ffab174d395e</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786146808</t>
+          <t>1786182455</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2.622951</t>
+          <t>15.395953</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,31 +1171,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x119ab2c3410b8d8f38cd160036d84db28ba2c49d7cebbdf58d09986906598c6e</t>
+          <t>0x201b1899dcc9e0afcf2abd8f2cdde8e12fd5b86f74a66f770f8ddc8a7cf491c3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5125</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1195,27 +1211,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
+          <t>0xf2c61359f7b4ce6fe2b13821af43c2179746ca09de07b69d73d4525126e1851d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,17 +1256,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786146807</t>
+          <t>1786181462</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3.570732</t>
+          <t>1.95599</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,31 +1283,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x0310cc4024f8c98d7c81dbc5746c8886ad1e2f2e8cb90d8cb5be5a6cfcc9c1a7</t>
+          <t>0x3bcefbdc10164bd825db264030b7e8cd91cc0a2aa40ab425adcfd968a7936a1f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.18934</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.2825</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Estrela Amadora +1</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1299,27 +1323,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x07271e150ddc345829a0b5bbafef14c0cfe914219f2ef99cfebbd564cae832a9</t>
+          <t>0x2507aa6dec45cb030bb997bd36241342522753b89a4fd11ab7aba981ce296e81</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,17 +1368,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786146807</t>
+          <t>1786181032</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3.755869</t>
+          <t>18.369345</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x5bca4d812a5a27b447581f4377300e300e467043d3e15730460fad09ad91080c</t>
+          <t>0x314dcaa3a3f4be8c4e673a3d25a8d43866eb82bdaa275e1830e16481e6b58fcc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1379,23 +1403,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>15.54313</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Asian Handicap (2)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Estrela Amadora +2</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1418,7 +1450,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
+          <t>0x3f96edde1005ba9d9c39379e32194aca486d726c35b7575193b798ad688ec098</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1448,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786138523</t>
+          <t>1786181032</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7.357664</t>
+          <t>26.233131</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,28 +1507,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
+          <t>0xdb8160bf95540a254ccbb6237d98812850293162110df9b9a6426eb0963856d7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>91.02352</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4688</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1507,27 +1539,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1552,17 +1584,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786135995</t>
+          <t>1786180032</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>194.183509</t>
+          <t>26.177515</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,59 +1611,67 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
+          <t>0x48fa0d4752b6415689691b258d9a00307dde4d81875d2eae9e278b85ee59a5ce</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>902.64812</t>
+          <t>15.19999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Asian Handicap (2)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Estrela Amadora +2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x3f96edde1005ba9d9c39379e32194aca486d726c35b7575193b798ad688ec098</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1656,17 +1696,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786135994</t>
+          <t>1786180032</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1930.798118</t>
+          <t>26.206879</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,31 +1723,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
+          <t>0x9a5ae871c88d1ea8948628be3580ebf41f4b3a99a6402fda21b17772df8cf6fd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.275</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Estrela Amadora +1</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1715,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x2507aa6dec45cb030bb997bd36241342522753b89a4fd11ab7aba981ce296e81</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1760,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786135800</t>
+          <t>1786179970</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>155.339806</t>
+          <t>16.327273</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,39 +1835,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
+          <t>0x11704d547b1815563cbcfd427f86f694149a2fb294772bc435a64f032e6f9535</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5.99999</t>
+          <t>11.94789</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6488</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -1827,27 +1867,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1872,17 +1912,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786135027</t>
+          <t>1786174340</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>9.248539</t>
+          <t>23.717896</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
+          <t>0xb33331a7c5dd3fa9ae4b279afdd5bd3f6795da10e428eef1cd4da6555f3d6f53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,12 +1950,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2475</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1931,27 +1971,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1976,17 +2016,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786134086</t>
+          <t>1786174324</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>9.010101</t>
+          <t>5.555556</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,31 +2043,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
+          <t>0xbcfad4be403d17328f68e33c671150e1aacf19949b68ac560e5aef53c0d366c5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Asian Handicap (2)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Estrela Amadora +2</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2035,27 +2083,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
+          <t>0x3f96edde1005ba9d9c39379e32194aca486d726c35b7575193b798ad688ec098</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2080,17 +2128,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786132603</t>
+          <t>1786172968</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>134.757282</t>
+          <t>62.914661</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,28 +2155,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
+          <t>0x485b8bc1c25c4435ab81832174033d2b5706d64c4bba55f1d5a3579aeb3b5cb8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>12.875</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2139,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
+          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2184,17 +2232,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786131718</t>
+          <t>1786165632</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>91.925466</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2211,39 +2259,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
+          <t>0x9d125073ec3f524cb81634bff9543957acd51d142414ae50799b56772cacc2b5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2525</t>
+          <t>1.1725</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2251,27 +2291,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2296,17 +2336,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786130523</t>
+          <t>1786161908</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>552.475248</t>
+          <t>12.985507</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,12 +2363,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
+          <t>0xd97957a2dbc75d4bbe2f8561247500721a9ccc599e0d1ddb1cb19dc3fc26b2c1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -2339,12 +2379,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5813</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2355,27 +2395,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x8c2bd7f367c91aaa67cce45975157c8fc230cd4f7dedf7ddf600e7b573e3ab54</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2400,17 +2440,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786130175</t>
+          <t>1786146808</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.72043</t>
+          <t>2.622951</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2427,28 +2467,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
+          <t>0x119ab2c3410b8d8f38cd160036d84db28ba2c49d7cebbdf58d09986906598c6e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>133.51</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.5125</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2459,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0xfe2fc99d42d480e8db751cacbc94deb354b2ee55330808b31961cbc103dcf9b9</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2504,17 +2544,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786129855</t>
+          <t>1786146807</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>193.492754</t>
+          <t>3.570732</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2531,39 +2571,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
+          <t>0x0310cc4024f8c98d7c81dbc5746c8886ad1e2f2e8cb90d8cb5be5a6cfcc9c1a7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.22719</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2571,27 +2603,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x07271e150ddc345829a0b5bbafef14c0cfe914219f2ef99cfebbd564cae832a9</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2616,17 +2648,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786129674</t>
+          <t>1786146807</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>3.197889</t>
+          <t>3.755869</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,39 +2675,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
+          <t>0x5bca4d812a5a27b447581f4377300e300e467043d3e15730460fad09ad91080c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -2683,27 +2707,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x9a7d3c7befcb0e3332400187e9d89517828f9845064f805a427856d29d793a85</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2728,17 +2752,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786129636</t>
+          <t>1786138523</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>13.029316</t>
+          <t>7.357664</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2755,28 +2779,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
+          <t>0xa9c88cc84caebd4ba3142a4ebf63e290208f354d9463b9004afb1166b7d8747f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>91.02352</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4688</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2802,7 +2826,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2832,7 +2856,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786129590</t>
+          <t>1786135995</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2842,7 +2866,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>22.150289</t>
+          <t>194.183509</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2859,28 +2883,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
+          <t>0x7e69c9c16087dc5311c73cf1cbf3ddbbe9ca48f3fcfed6a4defb00ff908db5c1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.16999</t>
+          <t>902.64812</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.6787</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2906,7 +2930,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2936,7 +2960,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786129160</t>
+          <t>1786135994</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2946,7 +2970,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>6.143632</t>
+          <t>1930.798118</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2963,28 +2987,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
+          <t>0x3aeca3698f17dbe5689cac38a65358f36dbf0292a1d42766168b5d5e8654a8c2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xeC1831f55CEcC9ed5971d87a8423414edb2e5A88</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25.5377</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3010,7 +3034,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3040,7 +3064,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786128775</t>
+          <t>1786135800</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3050,7 +3074,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>48.527696</t>
+          <t>155.339806</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3067,36 +3091,44 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
+          <t>0x3815710b5cec93e3437d2f896473827d258954dc4b7f2c0311afb6000dc60c9e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x5022174051792ac42d3af7Ff6bC9cf78a6aE3f32</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20.42793</t>
+          <t>5.99999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.6488</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
@@ -3114,7 +3146,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3144,7 +3176,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786128775</t>
+          <t>1786135027</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3154,7 +3186,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>38.817919</t>
+          <t>9.248539</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3171,28 +3203,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
+          <t>0xaf2ad3408d19dedbd2be619e663cc5247653766e71952626b3fa01be7191d3e3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.2475</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3218,7 +3250,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3248,7 +3280,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786128768</t>
+          <t>1786134086</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3258,7 +3290,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>9.691211</t>
+          <t>9.010101</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3275,28 +3307,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
+          <t>0x22cd9c5345775dbf34b8799b8321f8fc5cbeb4cffe25eba1339cdc156c539084</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3307,27 +3339,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0xdc18bb89a43247e2ed85a9facce4fa462f726aaed4e7e5f7bb15cdd0e83c27fd</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3352,17 +3384,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786128742</t>
+          <t>1786132603</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>46.645012</t>
+          <t>134.757282</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3379,44 +3411,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
+          <t>0xeecae1aefb7c1a529cdca14188c882feff52c72b5f52849ae62bd245267e4879</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10.60893</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Estoril 0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
@@ -3434,7 +3458,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
+          <t>0xcd3a93f244a9af6eff3a17273776a9a50f7e8f44547781d916193e7be19b4a18</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3464,7 +3488,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786128656</t>
+          <t>1786131718</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3474,7 +3498,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>21.650878</t>
+          <t>91.925466</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3491,12 +3515,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
+          <t>0xec2fd269b453b16057dd2a0d5c873cb70de333f5d134108cb5482d9e235e3cd8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xd8917E0f4fdb4E6F869bCAF1cF19a7FF38b8557e</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3506,22 +3530,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.2525</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3546,7 +3570,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3576,7 +3600,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786128630</t>
+          <t>1786130523</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3586,7 +3610,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>6.791171</t>
+          <t>552.475248</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3603,39 +3627,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
+          <t>0x6db1c7c0fa089b666e3e755e30a21e6835276ddeaea1e8fcb276b1ed14632051</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>64.79</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.5813</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -3658,7 +3674,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3688,7 +3704,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786128598</t>
+          <t>1786130175</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3698,7 +3714,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>1.72043</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3715,7 +3731,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
+          <t>0x48ccbf38a0310659ec2a678f3b6f94f811fb3fa845816ec494f83c962adcd2aa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3723,19 +3739,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>133.51</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3743,26 +3755,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -3800,7 +3808,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786127300</t>
+          <t>1786129855</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3810,7 +3818,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>40.939394</t>
+          <t>193.492754</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3827,7 +3835,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
+          <t>0x425b7722644eb6de45b5f7829b98c056da531b99b4c44527974a06ff1fe59eee</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3842,22 +3850,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.22719</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3325</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3882,7 +3890,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3912,7 +3920,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786127185</t>
+          <t>1786129674</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3922,7 +3930,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>7.548872</t>
+          <t>3.197889</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3939,12 +3947,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
+          <t>0xff23bdb33fc4aa108e4fb5baba5c468b12c2a4557c4fba69dc086d58351b2f12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3954,22 +3962,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3994,7 +4002,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4024,7 +4032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786127185</t>
+          <t>1786129636</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4034,7 +4042,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>4.325359</t>
+          <t>13.029316</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4051,28 +4059,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
+          <t>0x45c6c01c926cec0e208f55a2660bb6917e396693bb31fe6c9dff603d0a346082</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.1825</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4083,27 +4091,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
+          <t>0x7a878ce149185d9432458dfdf789ff934d35bd23042703a614fb4f599c5d3c1c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4128,17 +4136,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786126618</t>
+          <t>1786129590</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>117.808219</t>
+          <t>22.150289</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4155,39 +4163,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
+          <t>0x7944839f5a2b618b858a222f2d748cd93b6d3ea8ca8a6f6da198adfb33b795c0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7237f0dFfE03AEE905c24a69a6814a4D475Eb3e0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.16999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.6787</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786124013</t>
+          <t>1786129160</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>16.761905</t>
+          <t>6.143632</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4267,28 +4267,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
+          <t>0x77d3a4cd3bc4ab0a65d84182bdff411bad80a3e1d38b62e15d97197d8f0a5fb6</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>25.5377</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786123790</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>56.382353</t>
+          <t>48.527696</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4371,39 +4371,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
+          <t>0x11086c151792692f25f3c6cbdb42731e75f2f596eb02382409f55b8ac02d9181</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>20.42793</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2625</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4426,7 +4418,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4456,7 +4448,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786123308</t>
+          <t>1786128775</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4466,7 +4458,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>6.247619</t>
+          <t>38.817919</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4483,39 +4475,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
+          <t>0x7eff2c85674dd524b8272eeec121e550df683030f95acdad2b10f7722474a943</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Casa Pia</t>
-        </is>
-      </c>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -4523,27 +4507,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4568,17 +4552,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786114912</t>
+          <t>1786128768</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>7.363636</t>
+          <t>9.691211</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4595,28 +4579,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
+          <t>0x07edcb5c42f9afb12c1ac325ab1f0a2e908459ccb6f4b26b3915e6dca2800987</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>64.99</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4642,7 +4626,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4672,7 +4656,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786114872</t>
+          <t>1786128742</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4682,7 +4666,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>104.192385</t>
+          <t>46.645012</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4699,12 +4683,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
+          <t>0x7953d6084eb8f7520a44ea9ece56736e0c8faeba86401d5616e89fdf3b55d3b5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x09b3a190a1e971Dd0B4F82Eb9008287fe43a540C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4714,39 +4698,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10.60893</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Portugal Primeira Liga</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>Estoril 0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -4754,7 +4738,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x0dd3ff052dc243e76662f9ec9087976627171e44049811199743f41600a00538</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4784,7 +4768,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786112735</t>
+          <t>1786128656</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4794,7 +4778,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>3.088803</t>
+          <t>21.650878</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4811,12 +4795,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
+          <t>0x25b41924323a667f2381a21292974966a1cc15f4229682aca435133006ae6882</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4826,22 +4810,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4866,7 +4850,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4896,7 +4880,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786090860</t>
+          <t>1786128630</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4906,7 +4890,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>25.350211</t>
+          <t>6.791171</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4923,12 +4907,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
+          <t>0x8746b80116faa6e45a72f76560ad4102484a4b90af2f9b464891e5875a215b10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4938,39 +4922,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>64.79</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Famalicão</t>
@@ -4978,7 +4962,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
+          <t>0x68f8188aa9c0a032afc1f0d65f126f8a356816581fd353d250332ad4de46e5d5</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5008,7 +4992,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786089858</t>
+          <t>1786128598</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5018,7 +5002,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>11.019284</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5035,23 +5019,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
+          <t>0xa945dd8556b8ebec5ecf70c244545ccd2350ecb07edd2a1dd30b5e002b98dbf7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.07999</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.6238</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5059,7 +5047,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5067,27 +5059,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Maritimo vs Casa Pia</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19552012</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5112,17 +5104,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786085661</t>
+          <t>1786127300</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>4.93786</t>
+          <t>40.939394</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5139,12 +5131,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
+          <t>0xd5806889c21dcf7f88c46835450541eb6d81c060f4469f90c7681ec35696acd0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5154,22 +5146,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.3325</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5179,27 +5171,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
+          <t>0xed9e4cbcfdff1ec9ac389fb25d4c84a1faf2c925f7b5da82f5aa56cf5b643709</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5224,17 +5216,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786082857</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>86.956522</t>
+          <t>7.548872</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5251,12 +5243,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
+          <t>0x1c540d0e1a01bb28d103809e11ca77abbd29fc46a6578e3e6638022f7a184b99</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5266,22 +5258,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5291,27 +5283,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5336,17 +5328,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786082391</t>
+          <t>1786127185</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>155.918367</t>
+          <t>4.325359</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5363,27 +5355,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
+          <t>0x1062d6d808a20ac24f0e5a29be495e6545dbc80586f509e362534df3fddcf5b4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.0613</t>
+          <t>1.1825</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5391,11 +5379,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5403,27 +5387,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>FC Porto vs Alverca</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x18823ed6d251c8c4827e8f17f176126931f81a6804af4c7e515ff5e49d61593d</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516476</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5448,17 +5432,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786077443</t>
+          <t>1786126618</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786294800</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>130.612245</t>
+          <t>117.808219</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5475,31 +5459,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
+          <t>0x44803432d4e762ee2c6f38badc7718c7222fb5d533ec472754ee9a1bf5c56aae</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5507,27 +5499,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5552,17 +5544,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786076636</t>
+          <t>1786124013</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>16.761905</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5579,23 +5571,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
+          <t>0x43f21d40ac7db07c7ddf358ed265c1d9292941a718278fca3a7d22c1af575050</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>38.34</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5611,27 +5603,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5656,17 +5648,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786076571</t>
+          <t>1786123790</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>56.382353</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5683,31 +5675,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
+          <t>0x874a828e56878acbcb7d000cb369d977136f11df5c29519c076aa1c4998ca861</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.2625</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5715,27 +5715,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x22025701641811fa33c43a4d183fc3fc57e6e180fe4a86d01f1066496146939c</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5760,17 +5760,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786076507</t>
+          <t>1786123308</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>6.247619</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5787,23 +5787,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
+          <t>0x2d66959e74ab63c07d2e19f71c3f4b75e886f3f9f9c6a0a55c158ae3866a6579</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5811,7 +5815,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -5819,27 +5827,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x3cb3339529e9749918d3038b47a76339ee7067924669f602305a10be6fec203c</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5864,17 +5872,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786076442</t>
+          <t>1786114912</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>7.363636</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5891,23 +5899,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
+          <t>0xf6b180a0f4bb489299311fc5ab4ddc0f9f3cb476cc473feaeed126849ede3952</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>64.99</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5923,27 +5931,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5968,17 +5976,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786076377</t>
+          <t>1786114872</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>104.192385</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5995,23 +6003,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
+          <t>0xd05ecf3410440d330fbc8ee60a885cc25e411c04fe6040297d5e2e3a829952d1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6019,7 +6031,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6027,27 +6043,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6072,17 +6088,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786076312</t>
+          <t>1786112735</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>3.088803</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6099,23 +6115,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
+          <t>0x3b1e490b754fa31393f2d7a2ac5a6643a5389c998d8b9b488402ce2e8277e440</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6123,7 +6143,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6131,27 +6155,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6176,17 +6200,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786076247</t>
+          <t>1786090860</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>25.350211</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6203,31 +6227,39 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
+          <t>0x5f3aeeada41f86405f3653b66ee344430211c2201edb7f27c69a81b507a62671</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6235,27 +6267,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0x9bd57c98cbbe3e06a6f201fc351a1fb99a8ac8215e100584eaa510caf6ecfcfa</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6280,17 +6312,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786076181</t>
+          <t>1786089858</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>11.019284</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6307,23 +6339,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
+          <t>0x5db545e380a7c345262ca399edfaff705347dbe69e7662421c2cefb181c038a1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x7FBBAf1D0066D0f087b3686cAfd17b3B4A25Aa4b</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>3.07999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.6238</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6339,27 +6371,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Maritimo vs Casa Pia</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Maritimo</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xca3cb5ec3b3f53dda992d93b2a2b8df8c39690bca0b23ca6da1b5951a01855b6</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19552012</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6384,17 +6416,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786076117</t>
+          <t>1786085661</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>4.93786</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6411,23 +6443,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
+          <t>0xa0d51788e5508418113cdeaaaaabd6a1d6228c34290223cbdd343b540c546d49</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6435,7 +6471,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>FC Arouca</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6443,27 +6483,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Sporting Clube De Portugal CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+          <t>0xf17aa81af43e5328ecd75937871e6a591d9ea1f718250af6f636605eed85ea37</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19516479</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6488,17 +6528,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786076052</t>
+          <t>1786082857</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786217400</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>86.956522</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6515,23 +6555,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
+          <t>0x940b3d0a5f2c0d02aa00370958bd9a638dc2743fa86b198fc64dbf88b59fc4e4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>49.99996</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6539,7 +6583,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6592,7 +6640,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786075986</t>
+          <t>1786082391</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6602,7 +6650,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>52.98009</t>
+          <t>155.918367</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6619,23 +6667,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
+          <t>0xd4f4471b9a4cd078621001801a4f9664ae23bf39e508c64594c0b821861ba495</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>34.99996</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.9438</t>
+          <t>1.0613</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6643,7 +6695,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6696,7 +6752,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786075410</t>
+          <t>1786077443</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6706,7 +6762,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>37.08605</t>
+          <t>130.612245</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6723,27 +6779,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
+          <t>0x174cd45543aaf50bbbb7a07c8bd7b10d8cc42eda9c1477acb67588ce67012766</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6751,11 +6803,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6763,27 +6811,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6808,17 +6856,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786074828</t>
+          <t>1786076636</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>9.936508</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6835,27 +6883,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
+          <t>0x1c1eacde07c83070b93f5034bc7e9f27b7ba93e84081702d7cfc62e382a26a62</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10.8425</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.0388</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6863,11 +6907,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6875,27 +6915,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6920,17 +6960,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786054302</t>
+          <t>1786076571</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>279.806452</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6947,27 +6987,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
+          <t>0x63f0ea1366c58716b1045b45e4097f32f45940128a3dafca0951a7f24fa61f80</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6975,11 +7011,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -6987,27 +7019,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7032,17 +7064,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786053177</t>
+          <t>1786076507</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>11.619048</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7059,27 +7091,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
+          <t>0x4b2d4fb56a5ddac1aeba9d2899bed463f4500fc801f706f39e08458c3440cad8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7087,11 +7115,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7099,27 +7123,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7144,17 +7168,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786049713</t>
+          <t>1786076442</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>11.301587</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7171,23 +7195,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
+          <t>0xd721a7b395e52efed2aa009849853638b368e8d8fed200f138bf826b20f8bd94</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>165.96</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7203,27 +7227,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes vs FC Arouca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Vitoria Guimaraes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19516475</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7248,17 +7272,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786049379</t>
+          <t>1786076377</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786208400</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>340.430769</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7275,27 +7299,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
+          <t>0x457d97c5a72cfa7421cece30e9ae220d3f04c97cc6ea6fd38c666898f2ed0e04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.10054</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7303,11 +7323,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7315,27 +7331,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7360,17 +7376,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786048863</t>
+          <t>1786076312</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>3.76253</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7387,27 +7403,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
+          <t>0x40348d551ffd1a398437ebe036a60b0138f6e3d3deeeee860f1cbff818e3e2c8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.2925</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7415,11 +7427,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7427,27 +7435,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7472,17 +7480,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786048862</t>
+          <t>1786076247</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>34.188034</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7499,27 +7507,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+          <t>0x4f270ee3dc0a623c27e05ad5421e1236256f5e18848513e479a2f3f61b775ddf</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19.0949</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.0662</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7527,26 +7531,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>Estrela Amadora</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>Sporting Clube De Portugal CP</t>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786045554</t>
+          <t>1786076181</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>288.224906</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7611,39 +7611,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+          <t>0x8814c112ecc59039fb893698f2b7f7260002c6bff2969a32c396a28f6d216900</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7651,27 +7643,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7696,17 +7688,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786045527</t>
+          <t>1786076117</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>6.622785</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7723,27 +7715,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+          <t>0xd11995b1fc2a5b6a58a93db994a16829be4aca548d22c7b34a522bb24fad8b4f</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10.12292</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.0362</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7751,11 +7739,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Academico Viseu</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7763,27 +7747,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SL Benfica FC vs Academico Viseu</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>SL Benfica FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19551968</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7808,17 +7792,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786045134</t>
+          <t>1786076052</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786303800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>279.252966</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7835,23 +7819,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+          <t>0xc66d09d271e30a66de590c7b1c6d5ae45ea33b28a5247c347cba16ba98528641</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>49.99996</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7882,7 +7866,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7912,7 +7896,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786043934</t>
+          <t>1786075986</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7922,7 +7906,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>96.847059</t>
+          <t>52.98009</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7939,27 +7923,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+          <t>0xdf5fd611acbffce87f7b29174db70f70571979ee615ab031a925a05d1c86f71d</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>34.99996</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.0513</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7967,11 +7947,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Alverca</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -7979,27 +7955,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting Clube De Portugal CP</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516479</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8024,17 +8000,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786025695</t>
+          <t>1786075410</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786217400</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.08605</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8051,12 +8027,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+          <t>0x798392d3438dd61de66e0742a442cf8f3f97f7ec63181a2a338822f6427049fb</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8066,12 +8042,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.4125</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8081,32 +8057,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8136,7 +8112,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786015629</t>
+          <t>1786074828</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8146,7 +8122,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>19.345455</t>
+          <t>9.936508</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8163,23 +8139,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+          <t>0xcf652ab3194f9d567f6ddf3cdd019d440a65e8947d916dc3738e0335bbd3fe07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>10.8425</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.0388</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8187,7 +8167,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -8195,27 +8179,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>SL Benfica FC vs Academico Viseu</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>SL Benfica FC</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19551968</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8240,17 +8224,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785807147</t>
+          <t>1786054302</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786303800</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>279.806452</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8267,12 +8251,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+          <t>0xc6ee63bfb29ff37d865d39e8b8e92d29aa6d4569f5768aa6ccfbd9a9d9b5ea27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8282,12 +8266,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.0525</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8297,7 +8281,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8307,27 +8291,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>FC Porto vs Alverca</t>
+          <t>Estoril vs Famalicão</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19516476</t>
+          <t>L19516436</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8352,17 +8336,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785805367</t>
+          <t>1786053177</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1786294800</t>
+          <t>1786130100</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>28.761905</t>
+          <t>11.619048</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8379,23 +8363,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+          <t>0xeb3ffa21a81bad64e1c57daa8b3b700ccd2e0a139717709a792ed1a5fe326ca8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>70.81</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8403,7 +8391,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
@@ -8456,7 +8448,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785793268</t>
+          <t>1786049713</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8466,7 +8458,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>11.301587</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8483,23 +8475,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+          <t>0xcbddf823e635f74877809e664d307d69fbe07274867c3fdd6f6b327d9b61cfd2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>165.96</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8515,27 +8507,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Estoril vs Famalicão</t>
+          <t>Vitoria Guimaraes vs FC Arouca</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Vitoria Guimaraes</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+          <t>0x1952e4e0eea3adef3eef21ecd14324031f0ace6e12c2d14e6dd569d035162aa2</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19516436</t>
+          <t>L19516475</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8560,17 +8552,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785792146</t>
+          <t>1786049379</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>1786130100</t>
+          <t>1786208400</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1.383562</t>
+          <t>340.430769</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8587,12 +8579,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+          <t>0x141eb383c834f2311a0a971f6b102c95bbfbe72bf5aec96515326e8a44f36f73</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8602,12 +8594,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.10054</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8672,7 +8664,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785703082</t>
+          <t>1786048863</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8682,7 +8674,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>3.361345</t>
+          <t>3.76253</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8699,12 +8691,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+          <t>0x081ed159819d5a8a466bbae50bce4afd7d1ff9c80e37e3a8963dae2b0d164087</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8714,12 +8706,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.4512</t>
+          <t>1.2925</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8729,32 +8721,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Portugal Primeira Liga</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Estoril vs Famalicão</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Estoril</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Famalicão</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8784,7 +8776,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785702973</t>
+          <t>1786048862</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8794,7 +8786,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>3.168975</t>
+          <t>34.188034</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8811,110 +8803,1422 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>0xeadb7cbd384b3086a046b663a41d256f25782ec87a602e53327804ac26f8649e</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>19.0949</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.0662</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x5b64345975cf00da8fa2c970c0fa395244bae67afd8a6e447359e5785d80c172</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19516479</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1786045554</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1786217400</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>288.224906</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0xbd425b3af942b740eb524c67b09d901520f7e36f781edec39fe94f990058f28e</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.4937</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1786045527</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>6.622785</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x211e89a27cd857cfac01ad444d50285b78d7687ef94b8ec9d29ddf115e3f1b77</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>10.12292</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.0362</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>SL Benfica FC vs Academico Viseu</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>SL Benfica FC</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0x6bd6826ca8d748573498f2ac35a20fb5c9cd65be122b2d6bd4c3445f7d1f4f28</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19551968</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1786045134</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1786303800</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>279.252966</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0xeae7a78ab89105d02d28035125423525a0f8deab5d784f8092d1eae4a21a21ae</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>20.58</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.2125</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Estrela Amadora vs Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Sporting Clube De Portugal CP</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0x8240d316399f4df8430aecf2d4dff464b80ec9896c3e9a4a49cec6126730b286</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19516479</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1786043934</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1786217400</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>96.847059</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0x852ebe5fa56685e97646816bda03a75daa7be5c686a0c21e6cc91fe9e929156e</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.025</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.0513</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>FC Porto vs Alverca</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19516476</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1786025695</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1786294800</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0xfd9767efb72afaa140473f61906b464a888f1ccd0ce66296246c5feef22df0b4</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.4125</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1786015629</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>19.345455</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0xe1e981f73c1f5dcbea6fbe8985aac20970e24227fdd1722c2cabaf5ab34d5ffc</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1785807147</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0x86326082a40b8bd83786ee356714d61b0536794f55892123cc41ac2b3f486a09</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.0525</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>FC Porto vs Alverca</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0xdbac9a0b5328bd2f4a2e48e69be0724e79bc4a0ce6688099035cf63f6959d637</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19516476</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1785805367</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1786294800</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>28.761905</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0x3cfe50f74987860a9991087809d398727832f523a8592e4f716592807d1fcbcd</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>70.81</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1785793268</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0x091493eaabf18416d304e2afc51faef0752c61a5378ff4fde277854b3aca3087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0xd90f3a9796440faedb803c6686c8d8937f0ec27180a46805e5823a336f2caa7a</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1785792146</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1.383562</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0x6bd1b754d66093d507837af84d3bc61208561ca7bee41d496c52f24993630ac8</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0x048c07Af144F98F1c44E64455c69Cd7343116B71</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0x78d24a131bd50c9b54c26ebb579e3b5de696381c306e9696bdd139fe355424fa</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1785703082</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>3.361345</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0xbdb9c4454911d572e7daeae99f63956fc8a2f1036f88447c7a3be966b25dcfda</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.4512</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Portugal Primeira Liga</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Estoril vs Famalicão</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0xd1f6ef28397cea5e0fd8d621b5ffd5c7facb1e496cf5dffa97e30b23bb7ed538</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19516436</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1785702973</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1786130100</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>3.168975</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>0x25c79ef1a4efff81c8eacc6dd6166f75a9278fa2138727c677760b0010164ef9</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t>1.5225</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Portugal Primeira Liga</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>Estoril vs Famalicão</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Estoril</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>Famalicão</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>0x9928b6bf8cc196b9ef01e3d9935c418fd4ad023101bb76da4283e20916b1a22d</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>L19516436</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
         <is>
           <t>1785701935</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>1786130100</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>1.913876</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="V91" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
